--- a/Chapters/Chapter 1 - Fancy Designs/Fancy Weaves.xlsx
+++ b/Chapters/Chapter 1 - Fancy Designs/Fancy Weaves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fabric Structure and Design (FSD)\Chapters\Chapter 1 - Fancy Designs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7656F843-AD47-4417-84C6-0E345666B9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96FC8AA-C628-4B6E-968B-64008F08A9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="875" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Huckaback" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -221,6 +221,15 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>8=2x4</t>
+  </si>
+  <si>
+    <t>6=2x3</t>
+  </si>
+  <si>
+    <t>2x3x4=24</t>
+  </si>
 </sst>
 </file>
 
@@ -267,7 +276,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,8 +415,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -734,11 +755,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1079,6 +1115,45 @@
     <xf numFmtId="0" fontId="1" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1112,34 +1187,13 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2343,14 +2397,14 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="14"/>
-      <c r="Z14" s="114" t="s">
+      <c r="Z14" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="AA14" s="114"/>
-      <c r="AB14" s="114"/>
-      <c r="AC14" s="114"/>
-      <c r="AD14" s="114"/>
-      <c r="AE14" s="114"/>
+      <c r="AA14" s="127"/>
+      <c r="AB14" s="127"/>
+      <c r="AC14" s="127"/>
+      <c r="AD14" s="127"/>
+      <c r="AE14" s="127"/>
     </row>
     <row r="15" spans="3:39" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="3">
@@ -8591,25 +8645,25 @@
       <c r="DB19" s="1"/>
     </row>
     <row r="20" spans="6:106" x14ac:dyDescent="0.3">
-      <c r="G20" s="114" t="s">
+      <c r="G20" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="114"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="114"/>
-      <c r="AB20" s="114" t="s">
+      <c r="H20" s="127"/>
+      <c r="I20" s="127"/>
+      <c r="J20" s="127"/>
+      <c r="K20" s="127"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="127"/>
+      <c r="AB20" s="127" t="s">
         <v>44</v>
       </c>
-      <c r="AC20" s="114"/>
-      <c r="AD20" s="114"/>
-      <c r="AE20" s="114"/>
-      <c r="AF20" s="114"/>
-      <c r="AG20" s="114"/>
-      <c r="AH20" s="114"/>
-      <c r="AI20" s="114"/>
+      <c r="AC20" s="127"/>
+      <c r="AD20" s="127"/>
+      <c r="AE20" s="127"/>
+      <c r="AF20" s="127"/>
+      <c r="AG20" s="127"/>
+      <c r="AH20" s="127"/>
+      <c r="AI20" s="127"/>
       <c r="BS20" s="3">
         <v>11</v>
       </c>
@@ -8738,17 +8792,17 @@
       <c r="DB22" s="2"/>
     </row>
     <row r="23" spans="6:106" x14ac:dyDescent="0.3">
-      <c r="V23" s="126" t="s">
+      <c r="V23" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="W23" s="126"/>
-      <c r="X23" s="127"/>
-      <c r="Y23" s="127"/>
-      <c r="Z23" s="126" t="s">
+      <c r="W23" s="139"/>
+      <c r="X23" s="115"/>
+      <c r="Y23" s="115"/>
+      <c r="Z23" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="AA23" s="126"/>
-      <c r="AB23" s="127"/>
+      <c r="AA23" s="139"/>
+      <c r="AB23" s="115"/>
       <c r="BS23" s="3">
         <v>8</v>
       </c>
@@ -8800,13 +8854,13 @@
     </row>
     <row r="24" spans="6:106" x14ac:dyDescent="0.3">
       <c r="U24" s="1"/>
-      <c r="V24" s="128"/>
-      <c r="W24" s="128"/>
-      <c r="X24" s="129"/>
-      <c r="Y24" s="128"/>
-      <c r="Z24" s="129"/>
-      <c r="AA24" s="129"/>
-      <c r="AB24" s="129"/>
+      <c r="V24" s="116"/>
+      <c r="W24" s="116"/>
+      <c r="X24" s="117"/>
+      <c r="Y24" s="116"/>
+      <c r="Z24" s="117"/>
+      <c r="AA24" s="117"/>
+      <c r="AB24" s="117"/>
       <c r="AR24" s="56"/>
       <c r="AS24" s="56"/>
       <c r="AT24" s="56"/>
@@ -8857,13 +8911,13 @@
     </row>
     <row r="25" spans="6:106" x14ac:dyDescent="0.3">
       <c r="U25" s="2"/>
-      <c r="V25" s="128"/>
-      <c r="W25" s="129"/>
-      <c r="X25" s="129"/>
-      <c r="Y25" s="128"/>
-      <c r="Z25" s="128"/>
-      <c r="AA25" s="129"/>
-      <c r="AB25" s="128"/>
+      <c r="V25" s="116"/>
+      <c r="W25" s="117"/>
+      <c r="X25" s="117"/>
+      <c r="Y25" s="116"/>
+      <c r="Z25" s="116"/>
+      <c r="AA25" s="117"/>
+      <c r="AB25" s="116"/>
       <c r="AQ25" s="3">
         <v>5</v>
       </c>
@@ -8940,13 +8994,13 @@
     </row>
     <row r="26" spans="6:106" x14ac:dyDescent="0.3">
       <c r="U26" s="2"/>
-      <c r="V26" s="129"/>
-      <c r="W26" s="128"/>
-      <c r="X26" s="129"/>
-      <c r="Y26" s="128"/>
-      <c r="Z26" s="129"/>
-      <c r="AA26" s="128"/>
-      <c r="AB26" s="128"/>
+      <c r="V26" s="117"/>
+      <c r="W26" s="116"/>
+      <c r="X26" s="117"/>
+      <c r="Y26" s="116"/>
+      <c r="Z26" s="117"/>
+      <c r="AA26" s="116"/>
+      <c r="AB26" s="116"/>
       <c r="AQ26" s="3">
         <v>4</v>
       </c>
@@ -9024,13 +9078,13 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="U27" s="2"/>
-      <c r="V27" s="128"/>
-      <c r="W27" s="128"/>
-      <c r="X27" s="128"/>
-      <c r="Y27" s="129"/>
-      <c r="Z27" s="129"/>
-      <c r="AA27" s="129"/>
-      <c r="AB27" s="128"/>
+      <c r="V27" s="116"/>
+      <c r="W27" s="116"/>
+      <c r="X27" s="116"/>
+      <c r="Y27" s="117"/>
+      <c r="Z27" s="117"/>
+      <c r="AA27" s="117"/>
+      <c r="AB27" s="116"/>
       <c r="AO27" s="56"/>
       <c r="AP27" s="56"/>
       <c r="AQ27" s="3">
@@ -9121,13 +9175,13 @@
       <c r="R28" s="2"/>
       <c r="S28" s="1"/>
       <c r="U28" s="1"/>
-      <c r="V28" s="129"/>
-      <c r="W28" s="129"/>
-      <c r="X28" s="129"/>
-      <c r="Y28" s="128"/>
-      <c r="Z28" s="128"/>
-      <c r="AA28" s="128"/>
-      <c r="AB28" s="129"/>
+      <c r="V28" s="117"/>
+      <c r="W28" s="117"/>
+      <c r="X28" s="117"/>
+      <c r="Y28" s="116"/>
+      <c r="Z28" s="116"/>
+      <c r="AA28" s="116"/>
+      <c r="AB28" s="117"/>
       <c r="AQ28" s="3">
         <v>2</v>
       </c>
@@ -9205,13 +9259,13 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="U29" s="1"/>
-      <c r="V29" s="128"/>
-      <c r="W29" s="129"/>
-      <c r="X29" s="128"/>
-      <c r="Y29" s="129"/>
-      <c r="Z29" s="128"/>
-      <c r="AA29" s="129"/>
-      <c r="AB29" s="129"/>
+      <c r="V29" s="116"/>
+      <c r="W29" s="117"/>
+      <c r="X29" s="116"/>
+      <c r="Y29" s="117"/>
+      <c r="Z29" s="116"/>
+      <c r="AA29" s="117"/>
+      <c r="AB29" s="117"/>
       <c r="AQ29" s="3">
         <v>1</v>
       </c>
@@ -9300,13 +9354,13 @@
       <c r="R30" s="2"/>
       <c r="S30" s="1"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="129"/>
-      <c r="W30" s="128"/>
-      <c r="X30" s="128"/>
-      <c r="Y30" s="129"/>
-      <c r="Z30" s="129"/>
-      <c r="AA30" s="128"/>
-      <c r="AB30" s="129"/>
+      <c r="V30" s="117"/>
+      <c r="W30" s="116"/>
+      <c r="X30" s="116"/>
+      <c r="Y30" s="117"/>
+      <c r="Z30" s="117"/>
+      <c r="AA30" s="116"/>
+      <c r="AB30" s="117"/>
       <c r="AQ30" s="3" t="s">
         <v>0</v>
       </c>
@@ -9394,45 +9448,45 @@
       <c r="F31" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H31" s="130" t="s">
+      <c r="H31" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="I31" s="130"/>
-      <c r="J31" s="127"/>
-      <c r="K31" s="127"/>
-      <c r="L31" s="127"/>
-      <c r="M31" s="130" t="s">
+      <c r="I31" s="138"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="N31" s="130"/>
-      <c r="O31" s="127"/>
-      <c r="P31" s="127"/>
-      <c r="Q31" s="130" t="s">
+      <c r="N31" s="138"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="115"/>
+      <c r="Q31" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="R31" s="130"/>
+      <c r="R31" s="138"/>
       <c r="U31" s="2"/>
-      <c r="V31" s="129"/>
-      <c r="W31" s="129"/>
-      <c r="X31" s="128"/>
-      <c r="Y31" s="129"/>
-      <c r="Z31" s="128"/>
-      <c r="AA31" s="128"/>
-      <c r="AB31" s="128"/>
-      <c r="AR31" s="114" t="s">
+      <c r="V31" s="117"/>
+      <c r="W31" s="117"/>
+      <c r="X31" s="116"/>
+      <c r="Y31" s="117"/>
+      <c r="Z31" s="116"/>
+      <c r="AA31" s="116"/>
+      <c r="AB31" s="116"/>
+      <c r="AR31" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="AS31" s="114"/>
-      <c r="AT31" s="114"/>
-      <c r="AU31" s="114"/>
-      <c r="AV31" s="114"/>
-      <c r="AY31" s="114" t="s">
+      <c r="AS31" s="127"/>
+      <c r="AT31" s="127"/>
+      <c r="AU31" s="127"/>
+      <c r="AV31" s="127"/>
+      <c r="AY31" s="127" t="s">
         <v>47</v>
       </c>
-      <c r="AZ31" s="114"/>
-      <c r="BA31" s="114"/>
-      <c r="BB31" s="114"/>
-      <c r="BC31" s="114"/>
+      <c r="AZ31" s="127"/>
+      <c r="BA31" s="127"/>
+      <c r="BB31" s="127"/>
+      <c r="BC31" s="127"/>
       <c r="BJ31" s="3" t="s">
         <v>0</v>
       </c>
@@ -9537,39 +9591,39 @@
       </c>
     </row>
     <row r="32" spans="6:106" x14ac:dyDescent="0.3">
-      <c r="V32" s="130" t="s">
+      <c r="V32" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="W32" s="130"/>
-      <c r="X32" s="127"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="130" t="s">
+      <c r="W32" s="138"/>
+      <c r="X32" s="115"/>
+      <c r="Y32" s="115"/>
+      <c r="Z32" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="AA32" s="130"/>
-      <c r="AB32" s="127"/>
-      <c r="BK32" s="114" t="s">
+      <c r="AA32" s="138"/>
+      <c r="AB32" s="115"/>
+      <c r="BK32" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="BL32" s="114"/>
-      <c r="BM32" s="114"/>
-      <c r="BN32" s="114"/>
-      <c r="BO32" s="114"/>
-      <c r="BP32" s="114"/>
-      <c r="BT32" s="114" t="s">
+      <c r="BL32" s="127"/>
+      <c r="BM32" s="127"/>
+      <c r="BN32" s="127"/>
+      <c r="BO32" s="127"/>
+      <c r="BP32" s="127"/>
+      <c r="BT32" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="BU32" s="114"/>
-      <c r="BV32" s="114"/>
-      <c r="BW32" s="114"/>
-      <c r="BX32" s="114"/>
-      <c r="BY32" s="114"/>
-      <c r="BZ32" s="114"/>
-      <c r="CA32" s="114"/>
-      <c r="CB32" s="114"/>
-      <c r="CC32" s="114"/>
-      <c r="CD32" s="114"/>
-      <c r="CE32" s="114"/>
+      <c r="BU32" s="127"/>
+      <c r="BV32" s="127"/>
+      <c r="BW32" s="127"/>
+      <c r="BX32" s="127"/>
+      <c r="BY32" s="127"/>
+      <c r="BZ32" s="127"/>
+      <c r="CA32" s="127"/>
+      <c r="CB32" s="127"/>
+      <c r="CC32" s="127"/>
+      <c r="CD32" s="127"/>
+      <c r="CE32" s="127"/>
     </row>
     <row r="33" spans="2:80" x14ac:dyDescent="0.3">
       <c r="B33" s="56"/>
@@ -9929,13 +9983,13 @@
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
       <c r="W46" s="1"/>
-      <c r="AS46" s="114" t="s">
+      <c r="AS46" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="AT46" s="114"/>
-      <c r="AU46" s="114"/>
-      <c r="AV46" s="114"/>
-      <c r="AW46" s="114"/>
+      <c r="AT46" s="127"/>
+      <c r="AU46" s="127"/>
+      <c r="AV46" s="127"/>
+      <c r="AW46" s="127"/>
     </row>
     <row r="47" spans="2:80" x14ac:dyDescent="0.3">
       <c r="F47" s="3">
@@ -10082,77 +10136,77 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-      <c r="AE51" s="125"/>
+      <c r="AE51" s="114"/>
       <c r="AF51" s="1"/>
-      <c r="AG51" s="125"/>
-      <c r="AH51" s="125"/>
-      <c r="AI51" s="125"/>
+      <c r="AG51" s="114"/>
+      <c r="AH51" s="114"/>
+      <c r="AI51" s="114"/>
     </row>
     <row r="52" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="AB52" s="125"/>
+      <c r="AB52" s="114"/>
       <c r="AC52" s="1"/>
-      <c r="AD52" s="125"/>
-      <c r="AE52" s="125"/>
+      <c r="AD52" s="114"/>
+      <c r="AE52" s="114"/>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
-      <c r="AH52" s="125"/>
+      <c r="AH52" s="114"/>
       <c r="AI52" s="1"/>
     </row>
     <row r="53" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="AB53" s="125"/>
-      <c r="AC53" s="125"/>
+      <c r="AB53" s="114"/>
+      <c r="AC53" s="114"/>
       <c r="AD53" s="1"/>
-      <c r="AE53" s="125"/>
+      <c r="AE53" s="114"/>
       <c r="AF53" s="1"/>
-      <c r="AG53" s="125"/>
+      <c r="AG53" s="114"/>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
     </row>
     <row r="54" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="AB54" s="125"/>
+      <c r="AB54" s="114"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
-      <c r="AF54" s="125"/>
-      <c r="AG54" s="125"/>
-      <c r="AH54" s="125"/>
+      <c r="AF54" s="114"/>
+      <c r="AG54" s="114"/>
+      <c r="AH54" s="114"/>
       <c r="AI54" s="1"/>
     </row>
     <row r="55" spans="2:35" x14ac:dyDescent="0.3">
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
-      <c r="O55" s="125"/>
+      <c r="O55" s="114"/>
       <c r="P55" s="1"/>
-      <c r="Q55" s="125"/>
-      <c r="R55" s="125"/>
-      <c r="S55" s="125"/>
+      <c r="Q55" s="114"/>
+      <c r="R55" s="114"/>
+      <c r="S55" s="114"/>
       <c r="AB55" s="1"/>
-      <c r="AC55" s="125"/>
-      <c r="AD55" s="125"/>
-      <c r="AE55" s="125"/>
+      <c r="AC55" s="114"/>
+      <c r="AD55" s="114"/>
+      <c r="AE55" s="114"/>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
-      <c r="AI55" s="125"/>
+      <c r="AI55" s="114"/>
     </row>
     <row r="56" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="L56" s="125"/>
+      <c r="L56" s="114"/>
       <c r="M56" s="1"/>
-      <c r="N56" s="125"/>
-      <c r="O56" s="125"/>
+      <c r="N56" s="114"/>
+      <c r="O56" s="114"/>
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
-      <c r="R56" s="125"/>
+      <c r="R56" s="114"/>
       <c r="S56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
-      <c r="AD56" s="125"/>
+      <c r="AD56" s="114"/>
       <c r="AE56" s="1"/>
-      <c r="AF56" s="125"/>
+      <c r="AF56" s="114"/>
       <c r="AG56" s="1"/>
-      <c r="AH56" s="125"/>
-      <c r="AI56" s="125"/>
+      <c r="AH56" s="114"/>
+      <c r="AI56" s="114"/>
     </row>
     <row r="57" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B57" s="56"/>
@@ -10164,37 +10218,37 @@
       <c r="H57" s="56"/>
       <c r="I57" s="56"/>
       <c r="J57" s="56"/>
-      <c r="L57" s="125"/>
-      <c r="M57" s="125"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="114"/>
       <c r="N57" s="1"/>
-      <c r="O57" s="125"/>
+      <c r="O57" s="114"/>
       <c r="P57" s="1"/>
-      <c r="Q57" s="125"/>
+      <c r="Q57" s="114"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
       <c r="AB57" s="1"/>
-      <c r="AC57" s="125"/>
+      <c r="AC57" s="114"/>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1"/>
-      <c r="AF57" s="125"/>
-      <c r="AG57" s="125"/>
+      <c r="AF57" s="114"/>
+      <c r="AG57" s="114"/>
       <c r="AH57" s="1"/>
-      <c r="AI57" s="125"/>
+      <c r="AI57" s="114"/>
     </row>
     <row r="58" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="L58" s="125"/>
+      <c r="L58" s="114"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
-      <c r="P58" s="125"/>
-      <c r="Q58" s="125"/>
-      <c r="R58" s="125"/>
+      <c r="P58" s="114"/>
+      <c r="Q58" s="114"/>
+      <c r="R58" s="114"/>
       <c r="S58" s="1"/>
-      <c r="AB58" s="125"/>
-      <c r="AC58" s="125"/>
-      <c r="AD58" s="125"/>
+      <c r="AB58" s="114"/>
+      <c r="AC58" s="114"/>
+      <c r="AD58" s="114"/>
       <c r="AE58" s="1"/>
-      <c r="AF58" s="125"/>
+      <c r="AF58" s="114"/>
       <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
@@ -10215,10 +10269,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AY31:BC31"/>
-    <mergeCell ref="AR31:AV31"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="Z32:AA32"/>
     <mergeCell ref="AS46:AW46"/>
     <mergeCell ref="BK32:BP32"/>
     <mergeCell ref="BT32:CE32"/>
@@ -10229,6 +10279,10 @@
     <mergeCell ref="Q31:R31"/>
     <mergeCell ref="V23:W23"/>
     <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="AY31:BC31"/>
+    <mergeCell ref="AR31:AV31"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="Z32:AA32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11740,14 +11794,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:DB124"/>
+  <dimension ref="B2:FX161"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="106" width="3.21875" style="3" customWidth="1"/>
-    <col min="107" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="180" width="3.21875" style="3" customWidth="1"/>
+    <col min="181" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -11782,7 +11836,7 @@
       <c r="AR2" s="1"/>
       <c r="AS2" s="2"/>
     </row>
-    <row r="3" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
@@ -11817,7 +11871,7 @@
       <c r="AR3" s="2"/>
       <c r="AS3" s="1"/>
     </row>
-    <row r="4" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G4" s="3" t="s">
         <v>2</v>
       </c>
@@ -11852,7 +11906,7 @@
       <c r="AR4" s="1"/>
       <c r="AS4" s="1"/>
     </row>
-    <row r="5" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G5" s="3" t="s">
         <v>1</v>
       </c>
@@ -11887,7 +11941,7 @@
       <c r="AR5" s="2"/>
       <c r="AS5" s="1"/>
     </row>
-    <row r="6" spans="2:45" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:129" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="V6" s="1"/>
       <c r="W6" s="2"/>
       <c r="X6" s="1"/>
@@ -11913,7 +11967,7 @@
       <c r="AR6" s="1"/>
       <c r="AS6" s="2"/>
     </row>
-    <row r="7" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G7" s="3">
         <v>6</v>
       </c>
@@ -11952,7 +12006,7 @@
       <c r="AR7" s="2"/>
       <c r="AS7" s="1"/>
     </row>
-    <row r="8" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G8" s="3">
         <v>5</v>
       </c>
@@ -11990,8 +12044,31 @@
       <c r="AQ8" s="2"/>
       <c r="AR8" s="1"/>
       <c r="AS8" s="2"/>
-    </row>
-    <row r="9" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="BL8" s="1"/>
+      <c r="BM8" s="1"/>
+      <c r="BN8" s="1"/>
+      <c r="BO8" s="1"/>
+      <c r="BP8" s="2"/>
+      <c r="BQ8" s="1"/>
+      <c r="BR8" s="1"/>
+      <c r="BS8" s="1"/>
+      <c r="BT8" s="1"/>
+      <c r="BU8" s="2"/>
+      <c r="CU8" s="3">
+        <v>6</v>
+      </c>
+      <c r="CV8" s="121"/>
+      <c r="CW8" s="121"/>
+      <c r="CX8" s="121"/>
+      <c r="CY8" s="121"/>
+      <c r="CZ8" s="121"/>
+      <c r="DA8" s="122"/>
+      <c r="DB8" s="121"/>
+      <c r="DC8" s="121"/>
+      <c r="DD8" s="121"/>
+      <c r="DE8" s="121"/>
+    </row>
+    <row r="9" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G9" s="3">
         <v>4</v>
       </c>
@@ -12029,8 +12106,31 @@
       <c r="AQ9" s="1"/>
       <c r="AR9" s="2"/>
       <c r="AS9" s="1"/>
-    </row>
-    <row r="10" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="BL9" s="1"/>
+      <c r="BM9" s="1"/>
+      <c r="BN9" s="1"/>
+      <c r="BO9" s="2"/>
+      <c r="BP9" s="1"/>
+      <c r="BQ9" s="2"/>
+      <c r="BR9" s="1"/>
+      <c r="BS9" s="1"/>
+      <c r="BT9" s="1"/>
+      <c r="BU9" s="1"/>
+      <c r="CU9" s="3">
+        <v>5</v>
+      </c>
+      <c r="CV9" s="121"/>
+      <c r="CW9" s="121"/>
+      <c r="CX9" s="121"/>
+      <c r="CY9" s="121"/>
+      <c r="CZ9" s="122"/>
+      <c r="DA9" s="121"/>
+      <c r="DB9" s="122"/>
+      <c r="DC9" s="121"/>
+      <c r="DD9" s="121"/>
+      <c r="DE9" s="121"/>
+    </row>
+    <row r="10" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G10" s="3">
         <v>3</v>
       </c>
@@ -12068,8 +12168,31 @@
       <c r="AQ10" s="2"/>
       <c r="AR10" s="1"/>
       <c r="AS10" s="1"/>
-    </row>
-    <row r="11" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="BL10" s="1"/>
+      <c r="BM10" s="1"/>
+      <c r="BN10" s="2"/>
+      <c r="BO10" s="1"/>
+      <c r="BP10" s="1"/>
+      <c r="BQ10" s="1"/>
+      <c r="BR10" s="2"/>
+      <c r="BS10" s="1"/>
+      <c r="BT10" s="1"/>
+      <c r="BU10" s="1"/>
+      <c r="CU10" s="3">
+        <v>4</v>
+      </c>
+      <c r="CV10" s="121"/>
+      <c r="CW10" s="121"/>
+      <c r="CX10" s="121"/>
+      <c r="CY10" s="122"/>
+      <c r="CZ10" s="121"/>
+      <c r="DA10" s="121"/>
+      <c r="DB10" s="121"/>
+      <c r="DC10" s="122"/>
+      <c r="DD10" s="121"/>
+      <c r="DE10" s="121"/>
+    </row>
+    <row r="11" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G11" s="3">
         <v>2</v>
       </c>
@@ -12107,8 +12230,31 @@
       <c r="AQ11" s="1"/>
       <c r="AR11" s="2"/>
       <c r="AS11" s="1"/>
-    </row>
-    <row r="12" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="BL11" s="1"/>
+      <c r="BM11" s="2"/>
+      <c r="BN11" s="1"/>
+      <c r="BO11" s="1"/>
+      <c r="BP11" s="1"/>
+      <c r="BQ11" s="1"/>
+      <c r="BR11" s="1"/>
+      <c r="BS11" s="2"/>
+      <c r="BT11" s="1"/>
+      <c r="BU11" s="1"/>
+      <c r="CU11" s="3">
+        <v>3</v>
+      </c>
+      <c r="CV11" s="121"/>
+      <c r="CW11" s="121"/>
+      <c r="CX11" s="122"/>
+      <c r="CY11" s="121"/>
+      <c r="CZ11" s="121"/>
+      <c r="DA11" s="121"/>
+      <c r="DB11" s="121"/>
+      <c r="DC11" s="121"/>
+      <c r="DD11" s="122"/>
+      <c r="DE11" s="121"/>
+    </row>
+    <row r="12" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G12" s="3">
         <v>1</v>
       </c>
@@ -12146,8 +12292,31 @@
       <c r="AQ12" s="2"/>
       <c r="AR12" s="1"/>
       <c r="AS12" s="2"/>
-    </row>
-    <row r="13" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="BL12" s="2"/>
+      <c r="BM12" s="1"/>
+      <c r="BN12" s="1"/>
+      <c r="BO12" s="1"/>
+      <c r="BP12" s="1"/>
+      <c r="BQ12" s="1"/>
+      <c r="BR12" s="1"/>
+      <c r="BS12" s="1"/>
+      <c r="BT12" s="2"/>
+      <c r="BU12" s="1"/>
+      <c r="CU12" s="3">
+        <v>2</v>
+      </c>
+      <c r="CV12" s="121"/>
+      <c r="CW12" s="122"/>
+      <c r="CX12" s="121"/>
+      <c r="CY12" s="121"/>
+      <c r="CZ12" s="121"/>
+      <c r="DA12" s="121"/>
+      <c r="DB12" s="121"/>
+      <c r="DC12" s="121"/>
+      <c r="DD12" s="121"/>
+      <c r="DE12" s="122"/>
+    </row>
+    <row r="13" spans="2:129" x14ac:dyDescent="0.3">
       <c r="G13" s="3" t="s">
         <v>0</v>
       </c>
@@ -12205,8 +12374,21 @@
       <c r="AQ13" s="2"/>
       <c r="AR13" s="2"/>
       <c r="AS13" s="1"/>
-    </row>
-    <row r="14" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="CU13" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV13" s="122"/>
+      <c r="CW13" s="121"/>
+      <c r="CX13" s="121"/>
+      <c r="CY13" s="121"/>
+      <c r="CZ13" s="121"/>
+      <c r="DA13" s="121"/>
+      <c r="DB13" s="121"/>
+      <c r="DC13" s="121"/>
+      <c r="DD13" s="121"/>
+      <c r="DE13" s="121"/>
+    </row>
+    <row r="14" spans="2:129" x14ac:dyDescent="0.3">
       <c r="V14" s="1"/>
       <c r="W14" s="2"/>
       <c r="X14" s="1"/>
@@ -12231,8 +12413,33 @@
       <c r="AQ14" s="2"/>
       <c r="AR14" s="1"/>
       <c r="AS14" s="2"/>
-    </row>
-    <row r="15" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="BL14" s="1"/>
+      <c r="BM14" s="2"/>
+      <c r="BN14" s="2"/>
+      <c r="BO14" s="2"/>
+      <c r="BP14" s="2"/>
+      <c r="BQ14" s="2"/>
+      <c r="BR14" s="2"/>
+      <c r="BS14" s="2"/>
+      <c r="BT14" s="1"/>
+      <c r="BU14" s="2"/>
+      <c r="BW14" s="1"/>
+      <c r="BX14" s="2"/>
+      <c r="BY14" s="2"/>
+      <c r="BZ14" s="2"/>
+      <c r="CA14" s="2"/>
+      <c r="CC14" s="1"/>
+      <c r="CD14" s="2"/>
+      <c r="CE14" s="2"/>
+      <c r="CF14" s="2"/>
+      <c r="CG14" s="2"/>
+      <c r="CH14" s="2"/>
+      <c r="CI14" s="2"/>
+      <c r="CJ14" s="2"/>
+      <c r="CK14" s="1"/>
+      <c r="CL14" s="2"/>
+    </row>
+    <row r="15" spans="2:129" x14ac:dyDescent="0.3">
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="2"/>
@@ -12257,8 +12464,62 @@
       <c r="AQ15" s="1"/>
       <c r="AR15" s="2"/>
       <c r="AS15" s="1"/>
-    </row>
-    <row r="16" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="BL15" s="2"/>
+      <c r="BM15" s="1"/>
+      <c r="BN15" s="2"/>
+      <c r="BO15" s="2"/>
+      <c r="BP15" s="2"/>
+      <c r="BQ15" s="2"/>
+      <c r="BR15" s="2"/>
+      <c r="BS15" s="1"/>
+      <c r="BT15" s="2"/>
+      <c r="BU15" s="1"/>
+      <c r="BW15" s="2"/>
+      <c r="BX15" s="1"/>
+      <c r="BY15" s="2"/>
+      <c r="BZ15" s="2"/>
+      <c r="CA15" s="2"/>
+      <c r="CC15" s="2"/>
+      <c r="CD15" s="1"/>
+      <c r="CE15" s="2"/>
+      <c r="CF15" s="2"/>
+      <c r="CG15" s="2"/>
+      <c r="CH15" s="2"/>
+      <c r="CI15" s="2"/>
+      <c r="CJ15" s="1"/>
+      <c r="CK15" s="2"/>
+      <c r="CL15" s="1"/>
+      <c r="CU15" s="3">
+        <v>8</v>
+      </c>
+      <c r="CV15" s="1"/>
+      <c r="CW15" s="2"/>
+      <c r="CX15" s="1"/>
+      <c r="CY15" s="2"/>
+      <c r="CZ15" s="2"/>
+      <c r="DA15" s="2"/>
+      <c r="DB15" s="2"/>
+      <c r="DC15" s="2"/>
+      <c r="DD15" s="1"/>
+      <c r="DE15" s="2"/>
+      <c r="DG15" s="1"/>
+      <c r="DH15" s="2"/>
+      <c r="DI15" s="1"/>
+      <c r="DJ15" s="2"/>
+      <c r="DK15" s="2"/>
+      <c r="DL15" s="2"/>
+      <c r="DP15" s="1"/>
+      <c r="DQ15" s="2"/>
+      <c r="DR15" s="1"/>
+      <c r="DS15" s="2"/>
+      <c r="DT15" s="2"/>
+      <c r="DU15" s="2"/>
+      <c r="DV15" s="2"/>
+      <c r="DW15" s="2"/>
+      <c r="DX15" s="1"/>
+      <c r="DY15" s="2"/>
+    </row>
+    <row r="16" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>16</v>
       </c>
@@ -12302,8 +12563,62 @@
       <c r="AQ16" s="2"/>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
-    </row>
-    <row r="17" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="BL16" s="1"/>
+      <c r="BM16" s="2"/>
+      <c r="BN16" s="1"/>
+      <c r="BO16" s="2"/>
+      <c r="BP16" s="2"/>
+      <c r="BQ16" s="2"/>
+      <c r="BR16" s="1"/>
+      <c r="BS16" s="2"/>
+      <c r="BT16" s="1"/>
+      <c r="BU16" s="1"/>
+      <c r="BW16" s="1"/>
+      <c r="BX16" s="2"/>
+      <c r="BY16" s="1"/>
+      <c r="BZ16" s="2"/>
+      <c r="CA16" s="2"/>
+      <c r="CC16" s="1"/>
+      <c r="CD16" s="2"/>
+      <c r="CE16" s="1"/>
+      <c r="CF16" s="2"/>
+      <c r="CG16" s="2"/>
+      <c r="CH16" s="2"/>
+      <c r="CI16" s="1"/>
+      <c r="CJ16" s="2"/>
+      <c r="CK16" s="1"/>
+      <c r="CL16" s="1"/>
+      <c r="CU16" s="3">
+        <v>7</v>
+      </c>
+      <c r="CV16" s="1"/>
+      <c r="CW16" s="1"/>
+      <c r="CX16" s="2"/>
+      <c r="CY16" s="1"/>
+      <c r="CZ16" s="2"/>
+      <c r="DA16" s="2"/>
+      <c r="DB16" s="2"/>
+      <c r="DC16" s="1"/>
+      <c r="DD16" s="2"/>
+      <c r="DE16" s="1"/>
+      <c r="DG16" s="1"/>
+      <c r="DH16" s="1"/>
+      <c r="DI16" s="2"/>
+      <c r="DJ16" s="1"/>
+      <c r="DK16" s="2"/>
+      <c r="DL16" s="2"/>
+      <c r="DP16" s="1"/>
+      <c r="DQ16" s="1"/>
+      <c r="DR16" s="2"/>
+      <c r="DS16" s="1"/>
+      <c r="DT16" s="2"/>
+      <c r="DU16" s="2"/>
+      <c r="DV16" s="2"/>
+      <c r="DW16" s="1"/>
+      <c r="DX16" s="2"/>
+      <c r="DY16" s="1"/>
+    </row>
+    <row r="17" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f>B16-1</f>
         <v>15</v>
@@ -12348,8 +12663,62 @@
       <c r="AQ17" s="1"/>
       <c r="AR17" s="2"/>
       <c r="AS17" s="1"/>
-    </row>
-    <row r="18" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="BL17" s="1"/>
+      <c r="BM17" s="1"/>
+      <c r="BN17" s="2"/>
+      <c r="BO17" s="1"/>
+      <c r="BP17" s="2"/>
+      <c r="BQ17" s="1"/>
+      <c r="BR17" s="2"/>
+      <c r="BS17" s="1"/>
+      <c r="BT17" s="1"/>
+      <c r="BU17" s="1"/>
+      <c r="BW17" s="1"/>
+      <c r="BX17" s="1"/>
+      <c r="BY17" s="2"/>
+      <c r="BZ17" s="1"/>
+      <c r="CA17" s="2"/>
+      <c r="CC17" s="1"/>
+      <c r="CD17" s="1"/>
+      <c r="CE17" s="2"/>
+      <c r="CF17" s="1"/>
+      <c r="CG17" s="2"/>
+      <c r="CH17" s="1"/>
+      <c r="CI17" s="2"/>
+      <c r="CJ17" s="1"/>
+      <c r="CK17" s="1"/>
+      <c r="CL17" s="1"/>
+      <c r="CU17" s="3">
+        <v>6</v>
+      </c>
+      <c r="CV17" s="1"/>
+      <c r="CW17" s="1"/>
+      <c r="CX17" s="1"/>
+      <c r="CY17" s="2"/>
+      <c r="CZ17" s="1"/>
+      <c r="DA17" s="2"/>
+      <c r="DB17" s="1"/>
+      <c r="DC17" s="2"/>
+      <c r="DD17" s="1"/>
+      <c r="DE17" s="1"/>
+      <c r="DG17" s="1"/>
+      <c r="DH17" s="1"/>
+      <c r="DI17" s="1"/>
+      <c r="DJ17" s="2"/>
+      <c r="DK17" s="1"/>
+      <c r="DL17" s="2"/>
+      <c r="DP17" s="1"/>
+      <c r="DQ17" s="1"/>
+      <c r="DR17" s="1"/>
+      <c r="DS17" s="2"/>
+      <c r="DT17" s="1"/>
+      <c r="DU17" s="2"/>
+      <c r="DV17" s="1"/>
+      <c r="DW17" s="2"/>
+      <c r="DX17" s="1"/>
+      <c r="DY17" s="1"/>
+    </row>
+    <row r="18" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" ref="B18:B31" si="0">B17-1</f>
         <v>14</v>
@@ -12394,8 +12763,62 @@
       <c r="AQ18" s="2"/>
       <c r="AR18" s="1"/>
       <c r="AS18" s="2"/>
-    </row>
-    <row r="19" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="BL18" s="1"/>
+      <c r="BM18" s="1"/>
+      <c r="BN18" s="1"/>
+      <c r="BO18" s="2"/>
+      <c r="BP18" s="1"/>
+      <c r="BQ18" s="2"/>
+      <c r="BR18" s="1"/>
+      <c r="BS18" s="1"/>
+      <c r="BT18" s="1"/>
+      <c r="BU18" s="1"/>
+      <c r="BW18" s="1"/>
+      <c r="BX18" s="1"/>
+      <c r="BY18" s="1"/>
+      <c r="BZ18" s="2"/>
+      <c r="CA18" s="1"/>
+      <c r="CC18" s="1"/>
+      <c r="CD18" s="1"/>
+      <c r="CE18" s="1"/>
+      <c r="CF18" s="2"/>
+      <c r="CG18" s="1"/>
+      <c r="CH18" s="2"/>
+      <c r="CI18" s="1"/>
+      <c r="CJ18" s="1"/>
+      <c r="CK18" s="1"/>
+      <c r="CL18" s="1"/>
+      <c r="CU18" s="3">
+        <v>5</v>
+      </c>
+      <c r="CV18" s="1"/>
+      <c r="CW18" s="1"/>
+      <c r="CX18" s="1"/>
+      <c r="CY18" s="1"/>
+      <c r="CZ18" s="2"/>
+      <c r="DA18" s="1"/>
+      <c r="DB18" s="2"/>
+      <c r="DC18" s="1"/>
+      <c r="DD18" s="1"/>
+      <c r="DE18" s="1"/>
+      <c r="DG18" s="1"/>
+      <c r="DH18" s="1"/>
+      <c r="DI18" s="1"/>
+      <c r="DJ18" s="1"/>
+      <c r="DK18" s="2"/>
+      <c r="DL18" s="1"/>
+      <c r="DP18" s="1"/>
+      <c r="DQ18" s="1"/>
+      <c r="DR18" s="1"/>
+      <c r="DS18" s="1"/>
+      <c r="DT18" s="2"/>
+      <c r="DU18" s="1"/>
+      <c r="DV18" s="2"/>
+      <c r="DW18" s="1"/>
+      <c r="DX18" s="1"/>
+      <c r="DY18" s="1"/>
+    </row>
+    <row r="19" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -12440,8 +12863,62 @@
       <c r="AQ19" s="2"/>
       <c r="AR19" s="2"/>
       <c r="AS19" s="1"/>
-    </row>
-    <row r="20" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="BL19" s="1"/>
+      <c r="BM19" s="1"/>
+      <c r="BN19" s="2"/>
+      <c r="BO19" s="1"/>
+      <c r="BP19" s="2"/>
+      <c r="BQ19" s="1"/>
+      <c r="BR19" s="2"/>
+      <c r="BS19" s="1"/>
+      <c r="BT19" s="1"/>
+      <c r="BU19" s="1"/>
+      <c r="BW19" s="1"/>
+      <c r="BX19" s="1"/>
+      <c r="BY19" s="2"/>
+      <c r="BZ19" s="1"/>
+      <c r="CA19" s="2"/>
+      <c r="CC19" s="1"/>
+      <c r="CD19" s="1"/>
+      <c r="CE19" s="2"/>
+      <c r="CF19" s="1"/>
+      <c r="CG19" s="2"/>
+      <c r="CH19" s="1"/>
+      <c r="CI19" s="2"/>
+      <c r="CJ19" s="1"/>
+      <c r="CK19" s="1"/>
+      <c r="CL19" s="1"/>
+      <c r="CU19" s="3">
+        <v>4</v>
+      </c>
+      <c r="CV19" s="1"/>
+      <c r="CW19" s="1"/>
+      <c r="CX19" s="1"/>
+      <c r="CY19" s="2"/>
+      <c r="CZ19" s="1"/>
+      <c r="DA19" s="2"/>
+      <c r="DB19" s="1"/>
+      <c r="DC19" s="2"/>
+      <c r="DD19" s="1"/>
+      <c r="DE19" s="1"/>
+      <c r="DG19" s="1"/>
+      <c r="DH19" s="1"/>
+      <c r="DI19" s="1"/>
+      <c r="DJ19" s="2"/>
+      <c r="DK19" s="1"/>
+      <c r="DL19" s="2"/>
+      <c r="DP19" s="1"/>
+      <c r="DQ19" s="1"/>
+      <c r="DR19" s="1"/>
+      <c r="DS19" s="2"/>
+      <c r="DT19" s="1"/>
+      <c r="DU19" s="2"/>
+      <c r="DV19" s="1"/>
+      <c r="DW19" s="2"/>
+      <c r="DX19" s="1"/>
+      <c r="DY19" s="1"/>
+    </row>
+    <row r="20" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -12486,8 +12963,62 @@
       <c r="AQ20" s="2"/>
       <c r="AR20" s="1"/>
       <c r="AS20" s="2"/>
-    </row>
-    <row r="21" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="BL20" s="1"/>
+      <c r="BM20" s="2"/>
+      <c r="BN20" s="1"/>
+      <c r="BO20" s="2"/>
+      <c r="BP20" s="2"/>
+      <c r="BQ20" s="2"/>
+      <c r="BR20" s="1"/>
+      <c r="BS20" s="2"/>
+      <c r="BT20" s="1"/>
+      <c r="BU20" s="1"/>
+      <c r="BW20" s="1"/>
+      <c r="BX20" s="2"/>
+      <c r="BY20" s="1"/>
+      <c r="BZ20" s="2"/>
+      <c r="CA20" s="2"/>
+      <c r="CC20" s="1"/>
+      <c r="CD20" s="2"/>
+      <c r="CE20" s="1"/>
+      <c r="CF20" s="2"/>
+      <c r="CG20" s="2"/>
+      <c r="CH20" s="2"/>
+      <c r="CI20" s="1"/>
+      <c r="CJ20" s="2"/>
+      <c r="CK20" s="1"/>
+      <c r="CL20" s="1"/>
+      <c r="CU20" s="3">
+        <v>3</v>
+      </c>
+      <c r="CV20" s="1"/>
+      <c r="CW20" s="1"/>
+      <c r="CX20" s="2"/>
+      <c r="CY20" s="1"/>
+      <c r="CZ20" s="2"/>
+      <c r="DA20" s="2"/>
+      <c r="DB20" s="2"/>
+      <c r="DC20" s="1"/>
+      <c r="DD20" s="2"/>
+      <c r="DE20" s="1"/>
+      <c r="DG20" s="1"/>
+      <c r="DH20" s="1"/>
+      <c r="DI20" s="2"/>
+      <c r="DJ20" s="1"/>
+      <c r="DK20" s="2"/>
+      <c r="DL20" s="2"/>
+      <c r="DP20" s="1"/>
+      <c r="DQ20" s="1"/>
+      <c r="DR20" s="2"/>
+      <c r="DS20" s="1"/>
+      <c r="DT20" s="2"/>
+      <c r="DU20" s="2"/>
+      <c r="DV20" s="2"/>
+      <c r="DW20" s="1"/>
+      <c r="DX20" s="2"/>
+      <c r="DY20" s="1"/>
+    </row>
+    <row r="21" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -12532,8 +13063,62 @@
       <c r="AQ21" s="1"/>
       <c r="AR21" s="2"/>
       <c r="AS21" s="1"/>
-    </row>
-    <row r="22" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="BL21" s="2"/>
+      <c r="BM21" s="1"/>
+      <c r="BN21" s="2"/>
+      <c r="BO21" s="2"/>
+      <c r="BP21" s="2"/>
+      <c r="BQ21" s="2"/>
+      <c r="BR21" s="2"/>
+      <c r="BS21" s="1"/>
+      <c r="BT21" s="2"/>
+      <c r="BU21" s="1"/>
+      <c r="BW21" s="2"/>
+      <c r="BX21" s="1"/>
+      <c r="BY21" s="2"/>
+      <c r="BZ21" s="2"/>
+      <c r="CA21" s="2"/>
+      <c r="CC21" s="2"/>
+      <c r="CD21" s="1"/>
+      <c r="CE21" s="2"/>
+      <c r="CF21" s="2"/>
+      <c r="CG21" s="2"/>
+      <c r="CH21" s="2"/>
+      <c r="CI21" s="2"/>
+      <c r="CJ21" s="1"/>
+      <c r="CK21" s="2"/>
+      <c r="CL21" s="1"/>
+      <c r="CU21" s="3">
+        <v>2</v>
+      </c>
+      <c r="CV21" s="1"/>
+      <c r="CW21" s="2"/>
+      <c r="CX21" s="1"/>
+      <c r="CY21" s="2"/>
+      <c r="CZ21" s="2"/>
+      <c r="DA21" s="2"/>
+      <c r="DB21" s="2"/>
+      <c r="DC21" s="2"/>
+      <c r="DD21" s="1"/>
+      <c r="DE21" s="2"/>
+      <c r="DG21" s="1"/>
+      <c r="DH21" s="2"/>
+      <c r="DI21" s="1"/>
+      <c r="DJ21" s="2"/>
+      <c r="DK21" s="2"/>
+      <c r="DL21" s="2"/>
+      <c r="DP21" s="1"/>
+      <c r="DQ21" s="2"/>
+      <c r="DR21" s="1"/>
+      <c r="DS21" s="2"/>
+      <c r="DT21" s="2"/>
+      <c r="DU21" s="2"/>
+      <c r="DV21" s="2"/>
+      <c r="DW21" s="2"/>
+      <c r="DX21" s="1"/>
+      <c r="DY21" s="2"/>
+    </row>
+    <row r="22" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -12578,8 +13163,97 @@
       <c r="AQ22" s="2"/>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
-    </row>
-    <row r="23" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="BL22" s="3">
+        <v>1</v>
+      </c>
+      <c r="BM22" s="3">
+        <v>2</v>
+      </c>
+      <c r="BN22" s="3">
+        <v>3</v>
+      </c>
+      <c r="BO22" s="3">
+        <v>4</v>
+      </c>
+      <c r="BP22" s="3">
+        <v>5</v>
+      </c>
+      <c r="BQ22" s="3">
+        <v>6</v>
+      </c>
+      <c r="BR22" s="3">
+        <v>7</v>
+      </c>
+      <c r="BS22" s="3">
+        <v>8</v>
+      </c>
+      <c r="BT22" s="3">
+        <v>9</v>
+      </c>
+      <c r="BU22" s="3">
+        <v>10</v>
+      </c>
+      <c r="CC22" s="3">
+        <v>1</v>
+      </c>
+      <c r="CD22" s="3">
+        <v>2</v>
+      </c>
+      <c r="CE22" s="3">
+        <v>3</v>
+      </c>
+      <c r="CF22" s="3">
+        <v>4</v>
+      </c>
+      <c r="CG22" s="3">
+        <v>5</v>
+      </c>
+      <c r="CH22" s="3">
+        <v>6</v>
+      </c>
+      <c r="CI22" s="3">
+        <v>7</v>
+      </c>
+      <c r="CJ22" s="3">
+        <v>8</v>
+      </c>
+      <c r="CK22" s="3">
+        <v>9</v>
+      </c>
+      <c r="CL22" s="3">
+        <v>10</v>
+      </c>
+      <c r="CU22" s="3">
+        <v>1</v>
+      </c>
+      <c r="CV22" s="2"/>
+      <c r="CW22" s="1"/>
+      <c r="CX22" s="2"/>
+      <c r="CY22" s="2"/>
+      <c r="CZ22" s="2"/>
+      <c r="DA22" s="2"/>
+      <c r="DB22" s="2"/>
+      <c r="DC22" s="2"/>
+      <c r="DD22" s="2"/>
+      <c r="DE22" s="1"/>
+      <c r="DG22" s="2"/>
+      <c r="DH22" s="1"/>
+      <c r="DI22" s="2"/>
+      <c r="DJ22" s="2"/>
+      <c r="DK22" s="2"/>
+      <c r="DL22" s="2"/>
+      <c r="DP22" s="2"/>
+      <c r="DQ22" s="1"/>
+      <c r="DR22" s="2"/>
+      <c r="DS22" s="2"/>
+      <c r="DT22" s="2"/>
+      <c r="DU22" s="2"/>
+      <c r="DV22" s="2"/>
+      <c r="DW22" s="2"/>
+      <c r="DX22" s="2"/>
+      <c r="DY22" s="1"/>
+    </row>
+    <row r="23" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -12624,8 +13298,41 @@
       <c r="AQ23" s="1"/>
       <c r="AR23" s="2"/>
       <c r="AS23" s="1"/>
-    </row>
-    <row r="24" spans="2:67" x14ac:dyDescent="0.3">
+      <c r="CU23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="CV23" s="3">
+        <v>1</v>
+      </c>
+      <c r="CW23" s="3">
+        <v>2</v>
+      </c>
+      <c r="CX23" s="3">
+        <v>3</v>
+      </c>
+      <c r="CY23" s="3">
+        <v>4</v>
+      </c>
+      <c r="CZ23" s="3">
+        <v>5</v>
+      </c>
+      <c r="DA23" s="3">
+        <v>6</v>
+      </c>
+      <c r="DB23" s="3">
+        <v>7</v>
+      </c>
+      <c r="DC23" s="3">
+        <v>8</v>
+      </c>
+      <c r="DD23" s="3">
+        <v>9</v>
+      </c>
+      <c r="DE23" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -12671,7 +13378,7 @@
       <c r="AR24" s="1"/>
       <c r="AS24" s="2"/>
     </row>
-    <row r="25" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -12717,7 +13424,7 @@
       <c r="AR25" s="2"/>
       <c r="AS25" s="1"/>
     </row>
-    <row r="26" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -12739,7 +13446,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -12761,7 +13468,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12783,7 +13490,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12825,7 +13532,7 @@
       <c r="BN29" s="1"/>
       <c r="BO29" s="2"/>
     </row>
-    <row r="30" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12880,7 +13587,7 @@
       <c r="BN30" s="2"/>
       <c r="BO30" s="1"/>
     </row>
-    <row r="31" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B31" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12935,7 +13642,7 @@
       <c r="BN31" s="1"/>
       <c r="BO31" s="1"/>
     </row>
-    <row r="32" spans="2:67" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:129" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>0</v>
       </c>
@@ -13760,139 +14467,583 @@
       <c r="BN48" s="2"/>
       <c r="BO48" s="1"/>
     </row>
-    <row r="49" spans="11:106" x14ac:dyDescent="0.3">
-      <c r="CI49" s="1"/>
-      <c r="CJ49" s="2"/>
-      <c r="CK49" s="1"/>
-      <c r="CL49" s="2"/>
-      <c r="CM49" s="2"/>
-      <c r="CN49" s="2"/>
-      <c r="CO49" s="2"/>
-      <c r="CP49" s="2"/>
-      <c r="CQ49" s="1"/>
-      <c r="CR49" s="2"/>
-      <c r="CS49" s="1"/>
-      <c r="CT49" s="2"/>
-      <c r="CU49" s="1"/>
-      <c r="CV49" s="2"/>
-      <c r="CW49" s="2"/>
-      <c r="CX49" s="2"/>
-      <c r="CY49" s="2"/>
-      <c r="CZ49" s="2"/>
-      <c r="DA49" s="1"/>
-      <c r="DB49" s="2"/>
-    </row>
-    <row r="50" spans="11:106" x14ac:dyDescent="0.3">
-      <c r="CI50" s="1"/>
-      <c r="CJ50" s="1"/>
-      <c r="CK50" s="2"/>
-      <c r="CL50" s="1"/>
-      <c r="CM50" s="2"/>
-      <c r="CN50" s="2"/>
-      <c r="CO50" s="2"/>
-      <c r="CP50" s="1"/>
-      <c r="CQ50" s="2"/>
-      <c r="CR50" s="1"/>
-      <c r="CS50" s="1"/>
-      <c r="CT50" s="1"/>
-      <c r="CU50" s="2"/>
-      <c r="CV50" s="1"/>
-      <c r="CW50" s="2"/>
-      <c r="CX50" s="2"/>
-      <c r="CY50" s="2"/>
-      <c r="CZ50" s="1"/>
-      <c r="DA50" s="2"/>
-      <c r="DB50" s="1"/>
-    </row>
-    <row r="51" spans="11:106" x14ac:dyDescent="0.3">
-      <c r="CI51" s="1"/>
-      <c r="CJ51" s="1"/>
-      <c r="CK51" s="1"/>
-      <c r="CL51" s="2"/>
-      <c r="CM51" s="1"/>
-      <c r="CN51" s="2"/>
-      <c r="CO51" s="1"/>
-      <c r="CP51" s="2"/>
-      <c r="CQ51" s="1"/>
-      <c r="CR51" s="1"/>
-      <c r="CS51" s="1"/>
-      <c r="CT51" s="1"/>
-      <c r="CU51" s="1"/>
-      <c r="CV51" s="2"/>
-      <c r="CW51" s="1"/>
-      <c r="CX51" s="2"/>
-      <c r="CY51" s="1"/>
-      <c r="CZ51" s="2"/>
-      <c r="DA51" s="1"/>
-      <c r="DB51" s="1"/>
-    </row>
-    <row r="52" spans="11:106" x14ac:dyDescent="0.3">
-      <c r="CI52" s="1"/>
-      <c r="CJ52" s="1"/>
-      <c r="CK52" s="1"/>
-      <c r="CL52" s="1"/>
-      <c r="CM52" s="2"/>
-      <c r="CN52" s="1"/>
-      <c r="CO52" s="2"/>
-      <c r="CP52" s="1"/>
-      <c r="CQ52" s="1"/>
-      <c r="CR52" s="1"/>
-      <c r="CS52" s="1"/>
-      <c r="CT52" s="1"/>
-      <c r="CU52" s="1"/>
-      <c r="CV52" s="1"/>
-      <c r="CW52" s="2"/>
-      <c r="CX52" s="1"/>
-      <c r="CY52" s="2"/>
-      <c r="CZ52" s="1"/>
-      <c r="DA52" s="1"/>
-      <c r="DB52" s="1"/>
-    </row>
-    <row r="53" spans="11:106" x14ac:dyDescent="0.3">
-      <c r="CI53" s="1"/>
-      <c r="CJ53" s="1"/>
-      <c r="CK53" s="1"/>
-      <c r="CL53" s="2"/>
-      <c r="CM53" s="1"/>
-      <c r="CN53" s="2"/>
-      <c r="CO53" s="1"/>
-      <c r="CP53" s="2"/>
-      <c r="CQ53" s="1"/>
-      <c r="CR53" s="1"/>
-      <c r="CS53" s="1"/>
-      <c r="CT53" s="1"/>
-      <c r="CU53" s="1"/>
-      <c r="CV53" s="2"/>
-      <c r="CW53" s="1"/>
-      <c r="CX53" s="2"/>
-      <c r="CY53" s="1"/>
-      <c r="CZ53" s="2"/>
-      <c r="DA53" s="1"/>
-      <c r="DB53" s="1"/>
-    </row>
-    <row r="54" spans="11:106" x14ac:dyDescent="0.3">
-      <c r="CI54" s="1"/>
-      <c r="CJ54" s="1"/>
-      <c r="CK54" s="2"/>
-      <c r="CL54" s="1"/>
-      <c r="CM54" s="2"/>
-      <c r="CN54" s="2"/>
-      <c r="CO54" s="2"/>
-      <c r="CP54" s="1"/>
-      <c r="CQ54" s="2"/>
-      <c r="CR54" s="1"/>
-      <c r="CS54" s="1"/>
-      <c r="CT54" s="1"/>
-      <c r="CU54" s="2"/>
-      <c r="CV54" s="1"/>
-      <c r="CW54" s="2"/>
-      <c r="CX54" s="2"/>
-      <c r="CY54" s="2"/>
-      <c r="CZ54" s="1"/>
-      <c r="DA54" s="2"/>
-      <c r="DB54" s="1"/>
-    </row>
-    <row r="55" spans="11:106" x14ac:dyDescent="0.3">
+    <row r="49" spans="11:180" x14ac:dyDescent="0.3">
+      <c r="CI49" s="140"/>
+      <c r="CJ49" s="140"/>
+      <c r="CK49" s="140"/>
+      <c r="CL49" s="140"/>
+      <c r="CM49" s="140"/>
+      <c r="CN49" s="140"/>
+      <c r="CO49" s="140"/>
+      <c r="CP49" s="140"/>
+      <c r="CQ49" s="140"/>
+      <c r="CR49" s="140"/>
+      <c r="CS49" s="140"/>
+      <c r="CT49" s="140"/>
+      <c r="CU49" s="140"/>
+      <c r="CV49" s="140"/>
+      <c r="CW49" s="140"/>
+      <c r="CX49" s="140"/>
+      <c r="CY49" s="140"/>
+      <c r="CZ49" s="140"/>
+      <c r="DA49" s="140"/>
+      <c r="DB49" s="140"/>
+      <c r="DC49" s="140"/>
+      <c r="DD49" s="140"/>
+      <c r="DE49" s="140"/>
+      <c r="DF49" s="140"/>
+      <c r="DG49" s="140"/>
+      <c r="DH49" s="140"/>
+      <c r="DI49" s="140"/>
+      <c r="DJ49" s="140"/>
+      <c r="DK49" s="140"/>
+      <c r="DL49" s="140"/>
+      <c r="DM49" s="140"/>
+      <c r="DN49" s="140"/>
+      <c r="DO49" s="140"/>
+      <c r="DP49" s="140"/>
+      <c r="DQ49" s="140"/>
+      <c r="DR49" s="140"/>
+      <c r="DS49" s="140"/>
+      <c r="DT49" s="140"/>
+      <c r="DU49" s="140"/>
+      <c r="DV49" s="140"/>
+      <c r="DW49" s="140"/>
+      <c r="DX49" s="140"/>
+      <c r="DY49" s="140"/>
+      <c r="DZ49" s="140"/>
+      <c r="EA49" s="140"/>
+      <c r="EB49" s="140"/>
+      <c r="EC49" s="140"/>
+      <c r="ED49" s="140"/>
+      <c r="EE49" s="140"/>
+      <c r="EF49" s="140"/>
+      <c r="EG49" s="140"/>
+      <c r="EH49" s="140"/>
+      <c r="EI49" s="140"/>
+      <c r="EJ49" s="140"/>
+      <c r="EK49" s="140"/>
+      <c r="EL49" s="140"/>
+      <c r="EM49" s="140"/>
+      <c r="EN49" s="140"/>
+      <c r="EO49" s="140"/>
+      <c r="EP49" s="140"/>
+      <c r="EQ49" s="140"/>
+      <c r="ER49" s="140"/>
+      <c r="ES49" s="140"/>
+      <c r="ET49" s="140"/>
+      <c r="EU49" s="140"/>
+      <c r="EV49" s="140"/>
+      <c r="EW49" s="140"/>
+      <c r="EX49" s="140"/>
+      <c r="EY49" s="140"/>
+      <c r="EZ49" s="140"/>
+      <c r="FA49" s="140"/>
+      <c r="FB49" s="140"/>
+      <c r="FC49" s="140"/>
+      <c r="FD49" s="140"/>
+      <c r="FE49" s="140"/>
+      <c r="FF49" s="140"/>
+      <c r="FG49" s="140"/>
+      <c r="FH49" s="140"/>
+      <c r="FI49" s="140"/>
+      <c r="FJ49" s="140"/>
+      <c r="FK49" s="140"/>
+      <c r="FL49" s="140"/>
+      <c r="FM49" s="140"/>
+      <c r="FN49" s="140"/>
+      <c r="FO49" s="140"/>
+      <c r="FP49" s="140"/>
+      <c r="FQ49" s="140"/>
+      <c r="FR49" s="140"/>
+      <c r="FS49" s="140"/>
+      <c r="FT49" s="140"/>
+      <c r="FU49" s="140"/>
+      <c r="FV49" s="140"/>
+      <c r="FW49" s="140"/>
+      <c r="FX49" s="140"/>
+    </row>
+    <row r="50" spans="11:180" x14ac:dyDescent="0.3">
+      <c r="CI50" s="140"/>
+      <c r="CJ50" s="140"/>
+      <c r="CK50" s="140"/>
+      <c r="CL50" s="140"/>
+      <c r="CM50" s="140"/>
+      <c r="CN50" s="140"/>
+      <c r="CO50" s="140"/>
+      <c r="CP50" s="140"/>
+      <c r="CQ50" s="140"/>
+      <c r="CR50" s="140"/>
+      <c r="CS50" s="140"/>
+      <c r="CT50" s="140"/>
+      <c r="CU50" s="140"/>
+      <c r="CV50" s="140"/>
+      <c r="CW50" s="140"/>
+      <c r="CX50" s="140"/>
+      <c r="CY50" s="140"/>
+      <c r="CZ50" s="140"/>
+      <c r="DA50" s="140"/>
+      <c r="DB50" s="140"/>
+      <c r="DC50" s="140"/>
+      <c r="DD50" s="140"/>
+      <c r="DE50" s="140"/>
+      <c r="DF50" s="140"/>
+      <c r="DG50" s="140"/>
+      <c r="DH50" s="140"/>
+      <c r="DI50" s="140"/>
+      <c r="DJ50" s="140"/>
+      <c r="DK50" s="140"/>
+      <c r="DL50" s="140"/>
+      <c r="DM50" s="140"/>
+      <c r="DN50" s="140"/>
+      <c r="DO50" s="140"/>
+      <c r="DP50" s="140"/>
+      <c r="DQ50" s="140"/>
+      <c r="DR50" s="140"/>
+      <c r="DS50" s="140"/>
+      <c r="DT50" s="140"/>
+      <c r="DU50" s="140"/>
+      <c r="DV50" s="140"/>
+      <c r="DW50" s="140"/>
+      <c r="DX50" s="140"/>
+      <c r="DY50" s="140"/>
+      <c r="DZ50" s="140"/>
+      <c r="EA50" s="140"/>
+      <c r="EB50" s="140"/>
+      <c r="EC50" s="140"/>
+      <c r="ED50" s="140"/>
+      <c r="EE50" s="140"/>
+      <c r="EF50" s="140"/>
+      <c r="EG50" s="140"/>
+      <c r="EH50" s="140"/>
+      <c r="EI50" s="140"/>
+      <c r="EJ50" s="140"/>
+      <c r="EK50" s="140"/>
+      <c r="EL50" s="140"/>
+      <c r="EM50" s="140"/>
+      <c r="EN50" s="140"/>
+      <c r="EO50" s="140"/>
+      <c r="EP50" s="140"/>
+      <c r="EQ50" s="140"/>
+      <c r="ER50" s="140"/>
+      <c r="ES50" s="140"/>
+      <c r="ET50" s="140"/>
+      <c r="EU50" s="140"/>
+      <c r="EV50" s="140"/>
+      <c r="EW50" s="140"/>
+      <c r="EX50" s="140"/>
+      <c r="EY50" s="140"/>
+      <c r="EZ50" s="140"/>
+      <c r="FA50" s="140"/>
+      <c r="FB50" s="140"/>
+      <c r="FC50" s="140"/>
+      <c r="FD50" s="140"/>
+      <c r="FE50" s="140"/>
+      <c r="FF50" s="140"/>
+      <c r="FG50" s="140"/>
+      <c r="FH50" s="140"/>
+      <c r="FI50" s="140"/>
+      <c r="FJ50" s="140"/>
+      <c r="FK50" s="140"/>
+      <c r="FL50" s="140"/>
+      <c r="FM50" s="140"/>
+      <c r="FN50" s="140"/>
+      <c r="FO50" s="140"/>
+      <c r="FP50" s="140"/>
+      <c r="FQ50" s="140"/>
+      <c r="FR50" s="140"/>
+      <c r="FS50" s="140"/>
+      <c r="FT50" s="140"/>
+      <c r="FU50" s="140"/>
+      <c r="FV50" s="140"/>
+      <c r="FW50" s="140"/>
+      <c r="FX50" s="140"/>
+    </row>
+    <row r="51" spans="11:180" x14ac:dyDescent="0.3">
+      <c r="CI51" s="140"/>
+      <c r="CJ51" s="140"/>
+      <c r="CK51" s="140"/>
+      <c r="CL51" s="140"/>
+      <c r="CM51" s="140"/>
+      <c r="CN51" s="140"/>
+      <c r="CO51" s="140"/>
+      <c r="CP51" s="140"/>
+      <c r="CQ51" s="140"/>
+      <c r="CR51" s="140"/>
+      <c r="CS51" s="140"/>
+      <c r="CT51" s="140"/>
+      <c r="CU51" s="140"/>
+      <c r="CV51" s="140"/>
+      <c r="CW51" s="140"/>
+      <c r="CX51" s="140"/>
+      <c r="CY51" s="140"/>
+      <c r="CZ51" s="140"/>
+      <c r="DA51" s="140"/>
+      <c r="DB51" s="140"/>
+      <c r="DC51" s="140"/>
+      <c r="DD51" s="140"/>
+      <c r="DE51" s="140"/>
+      <c r="DF51" s="140"/>
+      <c r="DG51" s="140"/>
+      <c r="DH51" s="140"/>
+      <c r="DI51" s="140"/>
+      <c r="DJ51" s="140"/>
+      <c r="DK51" s="140"/>
+      <c r="DL51" s="140"/>
+      <c r="DM51" s="140"/>
+      <c r="DN51" s="140"/>
+      <c r="DO51" s="140"/>
+      <c r="DP51" s="140"/>
+      <c r="DQ51" s="140"/>
+      <c r="DR51" s="140"/>
+      <c r="DS51" s="140"/>
+      <c r="DT51" s="140"/>
+      <c r="DU51" s="140"/>
+      <c r="DV51" s="140"/>
+      <c r="DW51" s="140"/>
+      <c r="DX51" s="140"/>
+      <c r="DY51" s="140"/>
+      <c r="DZ51" s="140"/>
+      <c r="EA51" s="140"/>
+      <c r="EB51" s="140"/>
+      <c r="EC51" s="140"/>
+      <c r="ED51" s="140"/>
+      <c r="EE51" s="140"/>
+      <c r="EF51" s="140"/>
+      <c r="EG51" s="140"/>
+      <c r="EH51" s="140"/>
+      <c r="EI51" s="140"/>
+      <c r="EJ51" s="140"/>
+      <c r="EK51" s="140"/>
+      <c r="EL51" s="140"/>
+      <c r="EM51" s="140"/>
+      <c r="EN51" s="140"/>
+      <c r="EO51" s="140"/>
+      <c r="EP51" s="140"/>
+      <c r="EQ51" s="140"/>
+      <c r="ER51" s="140"/>
+      <c r="ES51" s="140"/>
+      <c r="ET51" s="140"/>
+      <c r="EU51" s="140"/>
+      <c r="EV51" s="140"/>
+      <c r="EW51" s="140"/>
+      <c r="EX51" s="140"/>
+      <c r="EY51" s="140"/>
+      <c r="EZ51" s="140"/>
+      <c r="FA51" s="140"/>
+      <c r="FB51" s="140"/>
+      <c r="FC51" s="140"/>
+      <c r="FD51" s="140"/>
+      <c r="FE51" s="140"/>
+      <c r="FF51" s="140"/>
+      <c r="FG51" s="140"/>
+      <c r="FH51" s="140"/>
+      <c r="FI51" s="140"/>
+      <c r="FJ51" s="140"/>
+      <c r="FK51" s="140"/>
+      <c r="FL51" s="140"/>
+      <c r="FM51" s="140"/>
+      <c r="FN51" s="140"/>
+      <c r="FO51" s="140"/>
+      <c r="FP51" s="140"/>
+      <c r="FQ51" s="140"/>
+      <c r="FR51" s="140"/>
+      <c r="FS51" s="140"/>
+      <c r="FT51" s="140"/>
+      <c r="FU51" s="140"/>
+      <c r="FV51" s="140"/>
+      <c r="FW51" s="140"/>
+      <c r="FX51" s="140"/>
+    </row>
+    <row r="52" spans="11:180" x14ac:dyDescent="0.3">
+      <c r="CI52" s="140"/>
+      <c r="CJ52" s="140"/>
+      <c r="CK52" s="140"/>
+      <c r="CL52" s="140"/>
+      <c r="CM52" s="140"/>
+      <c r="CN52" s="140"/>
+      <c r="CO52" s="140"/>
+      <c r="CP52" s="140"/>
+      <c r="CQ52" s="140"/>
+      <c r="CR52" s="140"/>
+      <c r="CS52" s="140"/>
+      <c r="CT52" s="140"/>
+      <c r="CU52" s="140"/>
+      <c r="CV52" s="140"/>
+      <c r="CW52" s="140"/>
+      <c r="CX52" s="140"/>
+      <c r="CY52" s="140"/>
+      <c r="CZ52" s="140"/>
+      <c r="DA52" s="140"/>
+      <c r="DB52" s="140"/>
+      <c r="DC52" s="140"/>
+      <c r="DD52" s="140"/>
+      <c r="DE52" s="140"/>
+      <c r="DF52" s="140"/>
+      <c r="DG52" s="140"/>
+      <c r="DH52" s="140"/>
+      <c r="DI52" s="140"/>
+      <c r="DJ52" s="140"/>
+      <c r="DK52" s="140"/>
+      <c r="DL52" s="140"/>
+      <c r="DM52" s="140"/>
+      <c r="DN52" s="140"/>
+      <c r="DO52" s="140"/>
+      <c r="DP52" s="140"/>
+      <c r="DQ52" s="140"/>
+      <c r="DR52" s="140"/>
+      <c r="DS52" s="140"/>
+      <c r="DT52" s="140"/>
+      <c r="DU52" s="140"/>
+      <c r="DV52" s="140"/>
+      <c r="DW52" s="140"/>
+      <c r="DX52" s="140"/>
+      <c r="DY52" s="140"/>
+      <c r="DZ52" s="140"/>
+      <c r="EA52" s="140"/>
+      <c r="EB52" s="140"/>
+      <c r="EC52" s="140"/>
+      <c r="ED52" s="140"/>
+      <c r="EE52" s="140"/>
+      <c r="EF52" s="140"/>
+      <c r="EG52" s="140"/>
+      <c r="EH52" s="140"/>
+      <c r="EI52" s="140"/>
+      <c r="EJ52" s="140"/>
+      <c r="EK52" s="140"/>
+      <c r="EL52" s="140"/>
+      <c r="EM52" s="140"/>
+      <c r="EN52" s="140"/>
+      <c r="EO52" s="140"/>
+      <c r="EP52" s="140"/>
+      <c r="EQ52" s="140"/>
+      <c r="ER52" s="140"/>
+      <c r="ES52" s="140"/>
+      <c r="ET52" s="140"/>
+      <c r="EU52" s="140"/>
+      <c r="EV52" s="140"/>
+      <c r="EW52" s="140"/>
+      <c r="EX52" s="140"/>
+      <c r="EY52" s="140"/>
+      <c r="EZ52" s="140"/>
+      <c r="FA52" s="140"/>
+      <c r="FB52" s="140"/>
+      <c r="FC52" s="140"/>
+      <c r="FD52" s="140"/>
+      <c r="FE52" s="140"/>
+      <c r="FF52" s="140"/>
+      <c r="FG52" s="140"/>
+      <c r="FH52" s="140"/>
+      <c r="FI52" s="140"/>
+      <c r="FJ52" s="140"/>
+      <c r="FK52" s="140"/>
+      <c r="FL52" s="140"/>
+      <c r="FM52" s="140"/>
+      <c r="FN52" s="140"/>
+      <c r="FO52" s="140"/>
+      <c r="FP52" s="140"/>
+      <c r="FQ52" s="140"/>
+      <c r="FR52" s="140"/>
+      <c r="FS52" s="140"/>
+      <c r="FT52" s="140"/>
+      <c r="FU52" s="140"/>
+      <c r="FV52" s="140"/>
+      <c r="FW52" s="140"/>
+      <c r="FX52" s="140"/>
+    </row>
+    <row r="53" spans="11:180" x14ac:dyDescent="0.3">
+      <c r="CI53" s="140"/>
+      <c r="CJ53" s="140"/>
+      <c r="CK53" s="140"/>
+      <c r="CL53" s="140"/>
+      <c r="CM53" s="140"/>
+      <c r="CN53" s="140"/>
+      <c r="CO53" s="140"/>
+      <c r="CP53" s="140"/>
+      <c r="CQ53" s="140"/>
+      <c r="CR53" s="140"/>
+      <c r="CS53" s="140"/>
+      <c r="CT53" s="140"/>
+      <c r="CU53" s="140"/>
+      <c r="CV53" s="140"/>
+      <c r="CW53" s="140"/>
+      <c r="CX53" s="140"/>
+      <c r="CY53" s="140"/>
+      <c r="CZ53" s="140"/>
+      <c r="DA53" s="140"/>
+      <c r="DB53" s="140"/>
+      <c r="DC53" s="140"/>
+      <c r="DD53" s="140"/>
+      <c r="DE53" s="140"/>
+      <c r="DF53" s="140"/>
+      <c r="DG53" s="140"/>
+      <c r="DH53" s="140"/>
+      <c r="DI53" s="140"/>
+      <c r="DJ53" s="140"/>
+      <c r="DK53" s="140"/>
+      <c r="DL53" s="140"/>
+      <c r="DM53" s="140"/>
+      <c r="DN53" s="140"/>
+      <c r="DO53" s="140"/>
+      <c r="DP53" s="140"/>
+      <c r="DQ53" s="140"/>
+      <c r="DR53" s="140"/>
+      <c r="DS53" s="140"/>
+      <c r="DT53" s="140"/>
+      <c r="DU53" s="140"/>
+      <c r="DV53" s="140"/>
+      <c r="DW53" s="140"/>
+      <c r="DX53" s="140"/>
+      <c r="DY53" s="140"/>
+      <c r="DZ53" s="140"/>
+      <c r="EA53" s="140"/>
+      <c r="EB53" s="140"/>
+      <c r="EC53" s="140"/>
+      <c r="ED53" s="140"/>
+      <c r="EE53" s="140"/>
+      <c r="EF53" s="140"/>
+      <c r="EG53" s="140"/>
+      <c r="EH53" s="140"/>
+      <c r="EI53" s="140"/>
+      <c r="EJ53" s="140"/>
+      <c r="EK53" s="140"/>
+      <c r="EL53" s="140"/>
+      <c r="EM53" s="140"/>
+      <c r="EN53" s="140"/>
+      <c r="EO53" s="140"/>
+      <c r="EP53" s="140"/>
+      <c r="EQ53" s="140"/>
+      <c r="ER53" s="140"/>
+      <c r="ES53" s="140"/>
+      <c r="ET53" s="140"/>
+      <c r="EU53" s="140"/>
+      <c r="EV53" s="140"/>
+      <c r="EW53" s="140"/>
+      <c r="EX53" s="140"/>
+      <c r="EY53" s="140"/>
+      <c r="EZ53" s="140"/>
+      <c r="FA53" s="140"/>
+      <c r="FB53" s="140"/>
+      <c r="FC53" s="140"/>
+      <c r="FD53" s="140"/>
+      <c r="FE53" s="140"/>
+      <c r="FF53" s="140"/>
+      <c r="FG53" s="140"/>
+      <c r="FH53" s="140"/>
+      <c r="FI53" s="140"/>
+      <c r="FJ53" s="140"/>
+      <c r="FK53" s="140"/>
+      <c r="FL53" s="140"/>
+      <c r="FM53" s="140"/>
+      <c r="FN53" s="140"/>
+      <c r="FO53" s="140"/>
+      <c r="FP53" s="140"/>
+      <c r="FQ53" s="140"/>
+      <c r="FR53" s="140"/>
+      <c r="FS53" s="140"/>
+      <c r="FT53" s="140"/>
+      <c r="FU53" s="140"/>
+      <c r="FV53" s="140"/>
+      <c r="FW53" s="140"/>
+      <c r="FX53" s="140"/>
+    </row>
+    <row r="54" spans="11:180" x14ac:dyDescent="0.3">
+      <c r="CI54" s="140"/>
+      <c r="CJ54" s="140"/>
+      <c r="CK54" s="140"/>
+      <c r="CL54" s="140"/>
+      <c r="CM54" s="140"/>
+      <c r="CN54" s="140"/>
+      <c r="CO54" s="140"/>
+      <c r="CP54" s="140"/>
+      <c r="CQ54" s="140"/>
+      <c r="CR54" s="140"/>
+      <c r="CS54" s="140"/>
+      <c r="CT54" s="140"/>
+      <c r="CU54" s="140"/>
+      <c r="CV54" s="140"/>
+      <c r="CW54" s="140"/>
+      <c r="CX54" s="140"/>
+      <c r="CY54" s="140"/>
+      <c r="CZ54" s="140"/>
+      <c r="DA54" s="140"/>
+      <c r="DB54" s="140"/>
+      <c r="DC54" s="140"/>
+      <c r="DD54" s="140"/>
+      <c r="DE54" s="140"/>
+      <c r="DF54" s="140"/>
+      <c r="DG54" s="140"/>
+      <c r="DH54" s="140"/>
+      <c r="DI54" s="140"/>
+      <c r="DJ54" s="140"/>
+      <c r="DK54" s="140"/>
+      <c r="DL54" s="140"/>
+      <c r="DM54" s="140"/>
+      <c r="DN54" s="140"/>
+      <c r="DO54" s="140"/>
+      <c r="DP54" s="140"/>
+      <c r="DQ54" s="140"/>
+      <c r="DR54" s="140"/>
+      <c r="DS54" s="140"/>
+      <c r="DT54" s="140"/>
+      <c r="DU54" s="140"/>
+      <c r="DV54" s="140"/>
+      <c r="DW54" s="140"/>
+      <c r="DX54" s="140"/>
+      <c r="DY54" s="140"/>
+      <c r="DZ54" s="140"/>
+      <c r="EA54" s="140"/>
+      <c r="EB54" s="140"/>
+      <c r="EC54" s="140"/>
+      <c r="ED54" s="140"/>
+      <c r="EE54" s="140"/>
+      <c r="EF54" s="140"/>
+      <c r="EG54" s="140"/>
+      <c r="EH54" s="140"/>
+      <c r="EI54" s="140"/>
+      <c r="EJ54" s="140"/>
+      <c r="EK54" s="140"/>
+      <c r="EL54" s="140"/>
+      <c r="EM54" s="140"/>
+      <c r="EN54" s="140"/>
+      <c r="EO54" s="140"/>
+      <c r="EP54" s="140"/>
+      <c r="EQ54" s="140"/>
+      <c r="ER54" s="140"/>
+      <c r="ES54" s="140"/>
+      <c r="ET54" s="140"/>
+      <c r="EU54" s="140"/>
+      <c r="EV54" s="140"/>
+      <c r="EW54" s="140"/>
+      <c r="EX54" s="140"/>
+      <c r="EY54" s="140"/>
+      <c r="EZ54" s="140"/>
+      <c r="FA54" s="140"/>
+      <c r="FB54" s="140"/>
+      <c r="FC54" s="140"/>
+      <c r="FD54" s="140"/>
+      <c r="FE54" s="140"/>
+      <c r="FF54" s="140"/>
+      <c r="FG54" s="140"/>
+      <c r="FH54" s="140"/>
+      <c r="FI54" s="140"/>
+      <c r="FJ54" s="140"/>
+      <c r="FK54" s="140"/>
+      <c r="FL54" s="140"/>
+      <c r="FM54" s="140"/>
+      <c r="FN54" s="140"/>
+      <c r="FO54" s="140"/>
+      <c r="FP54" s="140"/>
+      <c r="FQ54" s="140"/>
+      <c r="FR54" s="140"/>
+      <c r="FS54" s="140"/>
+      <c r="FT54" s="140"/>
+      <c r="FU54" s="140"/>
+      <c r="FV54" s="140"/>
+      <c r="FW54" s="140"/>
+      <c r="FX54" s="140"/>
+    </row>
+    <row r="55" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K55" s="3" t="s">
         <v>4</v>
       </c>
@@ -13902,28 +15053,102 @@
       <c r="O55" s="2"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
-      <c r="CI55" s="1"/>
-      <c r="CJ55" s="2"/>
-      <c r="CK55" s="1"/>
-      <c r="CL55" s="2"/>
-      <c r="CM55" s="2"/>
-      <c r="CN55" s="2"/>
-      <c r="CO55" s="2"/>
-      <c r="CP55" s="2"/>
-      <c r="CQ55" s="1"/>
-      <c r="CR55" s="2"/>
-      <c r="CS55" s="1"/>
-      <c r="CT55" s="2"/>
-      <c r="CU55" s="1"/>
-      <c r="CV55" s="2"/>
-      <c r="CW55" s="2"/>
-      <c r="CX55" s="2"/>
-      <c r="CY55" s="2"/>
-      <c r="CZ55" s="2"/>
-      <c r="DA55" s="1"/>
-      <c r="DB55" s="2"/>
-    </row>
-    <row r="56" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI55" s="140"/>
+      <c r="CJ55" s="140"/>
+      <c r="CK55" s="140"/>
+      <c r="CL55" s="140"/>
+      <c r="CM55" s="140"/>
+      <c r="CN55" s="140"/>
+      <c r="CO55" s="140"/>
+      <c r="CP55" s="140"/>
+      <c r="CQ55" s="140"/>
+      <c r="CR55" s="140"/>
+      <c r="CS55" s="140"/>
+      <c r="CT55" s="140"/>
+      <c r="CU55" s="140"/>
+      <c r="CV55" s="140"/>
+      <c r="CW55" s="140"/>
+      <c r="CX55" s="140"/>
+      <c r="CY55" s="140"/>
+      <c r="CZ55" s="140"/>
+      <c r="DA55" s="140"/>
+      <c r="DB55" s="140"/>
+      <c r="DC55" s="140"/>
+      <c r="DD55" s="140"/>
+      <c r="DE55" s="140"/>
+      <c r="DF55" s="140"/>
+      <c r="DG55" s="140"/>
+      <c r="DH55" s="140"/>
+      <c r="DI55" s="140"/>
+      <c r="DJ55" s="140"/>
+      <c r="DK55" s="140"/>
+      <c r="DL55" s="140"/>
+      <c r="DM55" s="140"/>
+      <c r="DN55" s="140"/>
+      <c r="DO55" s="140"/>
+      <c r="DP55" s="140"/>
+      <c r="DQ55" s="140"/>
+      <c r="DR55" s="140"/>
+      <c r="DS55" s="140"/>
+      <c r="DT55" s="140"/>
+      <c r="DU55" s="140"/>
+      <c r="DV55" s="140"/>
+      <c r="DW55" s="140"/>
+      <c r="DX55" s="140"/>
+      <c r="DY55" s="140"/>
+      <c r="DZ55" s="140"/>
+      <c r="EA55" s="140"/>
+      <c r="EB55" s="140"/>
+      <c r="EC55" s="140"/>
+      <c r="ED55" s="140"/>
+      <c r="EE55" s="140"/>
+      <c r="EF55" s="140"/>
+      <c r="EG55" s="140"/>
+      <c r="EH55" s="140"/>
+      <c r="EI55" s="140"/>
+      <c r="EJ55" s="140"/>
+      <c r="EK55" s="140"/>
+      <c r="EL55" s="140"/>
+      <c r="EM55" s="140"/>
+      <c r="EN55" s="140"/>
+      <c r="EO55" s="140"/>
+      <c r="EP55" s="140"/>
+      <c r="EQ55" s="140"/>
+      <c r="ER55" s="140"/>
+      <c r="ES55" s="140"/>
+      <c r="ET55" s="140"/>
+      <c r="EU55" s="140"/>
+      <c r="EV55" s="140"/>
+      <c r="EW55" s="140"/>
+      <c r="EX55" s="140"/>
+      <c r="EY55" s="140"/>
+      <c r="EZ55" s="140"/>
+      <c r="FA55" s="140"/>
+      <c r="FB55" s="140"/>
+      <c r="FC55" s="140"/>
+      <c r="FD55" s="140"/>
+      <c r="FE55" s="140"/>
+      <c r="FF55" s="140"/>
+      <c r="FG55" s="140"/>
+      <c r="FH55" s="140"/>
+      <c r="FI55" s="140"/>
+      <c r="FJ55" s="140"/>
+      <c r="FK55" s="140"/>
+      <c r="FL55" s="140"/>
+      <c r="FM55" s="140"/>
+      <c r="FN55" s="140"/>
+      <c r="FO55" s="140"/>
+      <c r="FP55" s="140"/>
+      <c r="FQ55" s="140"/>
+      <c r="FR55" s="140"/>
+      <c r="FS55" s="140"/>
+      <c r="FT55" s="140"/>
+      <c r="FU55" s="140"/>
+      <c r="FV55" s="140"/>
+      <c r="FW55" s="140"/>
+      <c r="FX55" s="140"/>
+    </row>
+    <row r="56" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K56" s="3" t="s">
         <v>3</v>
       </c>
@@ -13942,28 +15167,102 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
-      <c r="CI56" s="2"/>
-      <c r="CJ56" s="1"/>
-      <c r="CK56" s="2"/>
-      <c r="CL56" s="2"/>
-      <c r="CM56" s="2"/>
-      <c r="CN56" s="2"/>
-      <c r="CO56" s="2"/>
-      <c r="CP56" s="2"/>
-      <c r="CQ56" s="2"/>
-      <c r="CR56" s="1"/>
-      <c r="CS56" s="2"/>
-      <c r="CT56" s="1"/>
-      <c r="CU56" s="2"/>
-      <c r="CV56" s="2"/>
-      <c r="CW56" s="2"/>
-      <c r="CX56" s="2"/>
-      <c r="CY56" s="2"/>
-      <c r="CZ56" s="2"/>
-      <c r="DA56" s="2"/>
-      <c r="DB56" s="1"/>
-    </row>
-    <row r="57" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI56" s="140"/>
+      <c r="CJ56" s="140"/>
+      <c r="CK56" s="140"/>
+      <c r="CL56" s="140"/>
+      <c r="CM56" s="140"/>
+      <c r="CN56" s="140"/>
+      <c r="CO56" s="140"/>
+      <c r="CP56" s="140"/>
+      <c r="CQ56" s="140"/>
+      <c r="CR56" s="140"/>
+      <c r="CS56" s="140"/>
+      <c r="CT56" s="140"/>
+      <c r="CU56" s="140"/>
+      <c r="CV56" s="140"/>
+      <c r="CW56" s="140"/>
+      <c r="CX56" s="140"/>
+      <c r="CY56" s="140"/>
+      <c r="CZ56" s="140"/>
+      <c r="DA56" s="140"/>
+      <c r="DB56" s="140"/>
+      <c r="DC56" s="140"/>
+      <c r="DD56" s="140"/>
+      <c r="DE56" s="140"/>
+      <c r="DF56" s="140"/>
+      <c r="DG56" s="140"/>
+      <c r="DH56" s="140"/>
+      <c r="DI56" s="140"/>
+      <c r="DJ56" s="140"/>
+      <c r="DK56" s="140"/>
+      <c r="DL56" s="140"/>
+      <c r="DM56" s="140"/>
+      <c r="DN56" s="140"/>
+      <c r="DO56" s="140"/>
+      <c r="DP56" s="140"/>
+      <c r="DQ56" s="140"/>
+      <c r="DR56" s="140"/>
+      <c r="DS56" s="140"/>
+      <c r="DT56" s="140"/>
+      <c r="DU56" s="140"/>
+      <c r="DV56" s="140"/>
+      <c r="DW56" s="140"/>
+      <c r="DX56" s="140"/>
+      <c r="DY56" s="140"/>
+      <c r="DZ56" s="140"/>
+      <c r="EA56" s="140"/>
+      <c r="EB56" s="140"/>
+      <c r="EC56" s="140"/>
+      <c r="ED56" s="140"/>
+      <c r="EE56" s="140"/>
+      <c r="EF56" s="140"/>
+      <c r="EG56" s="140"/>
+      <c r="EH56" s="140"/>
+      <c r="EI56" s="140"/>
+      <c r="EJ56" s="140"/>
+      <c r="EK56" s="140"/>
+      <c r="EL56" s="140"/>
+      <c r="EM56" s="140"/>
+      <c r="EN56" s="140"/>
+      <c r="EO56" s="140"/>
+      <c r="EP56" s="140"/>
+      <c r="EQ56" s="140"/>
+      <c r="ER56" s="140"/>
+      <c r="ES56" s="140"/>
+      <c r="ET56" s="140"/>
+      <c r="EU56" s="140"/>
+      <c r="EV56" s="140"/>
+      <c r="EW56" s="140"/>
+      <c r="EX56" s="140"/>
+      <c r="EY56" s="140"/>
+      <c r="EZ56" s="140"/>
+      <c r="FA56" s="140"/>
+      <c r="FB56" s="140"/>
+      <c r="FC56" s="140"/>
+      <c r="FD56" s="140"/>
+      <c r="FE56" s="140"/>
+      <c r="FF56" s="140"/>
+      <c r="FG56" s="140"/>
+      <c r="FH56" s="140"/>
+      <c r="FI56" s="140"/>
+      <c r="FJ56" s="140"/>
+      <c r="FK56" s="140"/>
+      <c r="FL56" s="140"/>
+      <c r="FM56" s="140"/>
+      <c r="FN56" s="140"/>
+      <c r="FO56" s="140"/>
+      <c r="FP56" s="140"/>
+      <c r="FQ56" s="140"/>
+      <c r="FR56" s="140"/>
+      <c r="FS56" s="140"/>
+      <c r="FT56" s="140"/>
+      <c r="FU56" s="140"/>
+      <c r="FV56" s="140"/>
+      <c r="FW56" s="140"/>
+      <c r="FX56" s="140"/>
+    </row>
+    <row r="57" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K57" s="3" t="s">
         <v>2</v>
       </c>
@@ -13995,28 +15294,102 @@
       <c r="BY57" s="2"/>
       <c r="BZ57" s="1"/>
       <c r="CA57" s="2"/>
-      <c r="CI57" s="1"/>
-      <c r="CJ57" s="2"/>
-      <c r="CK57" s="1"/>
-      <c r="CL57" s="2"/>
-      <c r="CM57" s="2"/>
-      <c r="CN57" s="2"/>
-      <c r="CO57" s="2"/>
-      <c r="CP57" s="2"/>
-      <c r="CQ57" s="1"/>
-      <c r="CR57" s="2"/>
-      <c r="CS57" s="1"/>
-      <c r="CT57" s="2"/>
-      <c r="CU57" s="1"/>
-      <c r="CV57" s="2"/>
-      <c r="CW57" s="2"/>
-      <c r="CX57" s="2"/>
-      <c r="CY57" s="2"/>
-      <c r="CZ57" s="2"/>
-      <c r="DA57" s="1"/>
-      <c r="DB57" s="2"/>
-    </row>
-    <row r="58" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI57" s="140"/>
+      <c r="CJ57" s="140"/>
+      <c r="CK57" s="140"/>
+      <c r="CL57" s="140"/>
+      <c r="CM57" s="140"/>
+      <c r="CN57" s="140"/>
+      <c r="CO57" s="140"/>
+      <c r="CP57" s="140"/>
+      <c r="CQ57" s="140"/>
+      <c r="CR57" s="140"/>
+      <c r="CS57" s="140"/>
+      <c r="CT57" s="140"/>
+      <c r="CU57" s="140"/>
+      <c r="CV57" s="140"/>
+      <c r="CW57" s="140"/>
+      <c r="CX57" s="140"/>
+      <c r="CY57" s="140"/>
+      <c r="CZ57" s="140"/>
+      <c r="DA57" s="140"/>
+      <c r="DB57" s="140"/>
+      <c r="DC57" s="140"/>
+      <c r="DD57" s="140"/>
+      <c r="DE57" s="140"/>
+      <c r="DF57" s="140"/>
+      <c r="DG57" s="140"/>
+      <c r="DH57" s="140"/>
+      <c r="DI57" s="140"/>
+      <c r="DJ57" s="140"/>
+      <c r="DK57" s="140"/>
+      <c r="DL57" s="140"/>
+      <c r="DM57" s="140"/>
+      <c r="DN57" s="140"/>
+      <c r="DO57" s="140"/>
+      <c r="DP57" s="140"/>
+      <c r="DQ57" s="140"/>
+      <c r="DR57" s="140"/>
+      <c r="DS57" s="140"/>
+      <c r="DT57" s="140"/>
+      <c r="DU57" s="140"/>
+      <c r="DV57" s="140"/>
+      <c r="DW57" s="140"/>
+      <c r="DX57" s="140"/>
+      <c r="DY57" s="140"/>
+      <c r="DZ57" s="140"/>
+      <c r="EA57" s="140"/>
+      <c r="EB57" s="140"/>
+      <c r="EC57" s="140"/>
+      <c r="ED57" s="140"/>
+      <c r="EE57" s="140"/>
+      <c r="EF57" s="140"/>
+      <c r="EG57" s="140"/>
+      <c r="EH57" s="140"/>
+      <c r="EI57" s="140"/>
+      <c r="EJ57" s="140"/>
+      <c r="EK57" s="140"/>
+      <c r="EL57" s="140"/>
+      <c r="EM57" s="140"/>
+      <c r="EN57" s="140"/>
+      <c r="EO57" s="140"/>
+      <c r="EP57" s="140"/>
+      <c r="EQ57" s="140"/>
+      <c r="ER57" s="140"/>
+      <c r="ES57" s="140"/>
+      <c r="ET57" s="140"/>
+      <c r="EU57" s="140"/>
+      <c r="EV57" s="140"/>
+      <c r="EW57" s="140"/>
+      <c r="EX57" s="140"/>
+      <c r="EY57" s="140"/>
+      <c r="EZ57" s="140"/>
+      <c r="FA57" s="140"/>
+      <c r="FB57" s="140"/>
+      <c r="FC57" s="140"/>
+      <c r="FD57" s="140"/>
+      <c r="FE57" s="140"/>
+      <c r="FF57" s="140"/>
+      <c r="FG57" s="140"/>
+      <c r="FH57" s="140"/>
+      <c r="FI57" s="140"/>
+      <c r="FJ57" s="140"/>
+      <c r="FK57" s="140"/>
+      <c r="FL57" s="140"/>
+      <c r="FM57" s="140"/>
+      <c r="FN57" s="140"/>
+      <c r="FO57" s="140"/>
+      <c r="FP57" s="140"/>
+      <c r="FQ57" s="140"/>
+      <c r="FR57" s="140"/>
+      <c r="FS57" s="140"/>
+      <c r="FT57" s="140"/>
+      <c r="FU57" s="140"/>
+      <c r="FV57" s="140"/>
+      <c r="FW57" s="140"/>
+      <c r="FX57" s="140"/>
+    </row>
+    <row r="58" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K58" s="3" t="s">
         <v>1</v>
       </c>
@@ -14035,19 +15408,6 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="2"/>
       <c r="AD58" s="1"/>
-      <c r="AN58" s="3">
-        <v>8</v>
-      </c>
-      <c r="AO58" s="1"/>
-      <c r="AP58" s="2"/>
-      <c r="AQ58" s="1"/>
-      <c r="AR58" s="2"/>
-      <c r="AS58" s="2"/>
-      <c r="AT58" s="2"/>
-      <c r="AU58" s="2"/>
-      <c r="AV58" s="2"/>
-      <c r="AW58" s="1"/>
-      <c r="AX58" s="2"/>
       <c r="BQ58" s="3">
         <v>7</v>
       </c>
@@ -14061,41 +15421,102 @@
       <c r="BY58" s="1"/>
       <c r="BZ58" s="2"/>
       <c r="CA58" s="1"/>
-      <c r="CI58" s="1"/>
-      <c r="CJ58" s="1"/>
-      <c r="CK58" s="2"/>
-      <c r="CL58" s="1"/>
-      <c r="CM58" s="2"/>
-      <c r="CN58" s="2"/>
-      <c r="CO58" s="2"/>
-      <c r="CP58" s="1"/>
-      <c r="CQ58" s="2"/>
-      <c r="CR58" s="1"/>
-      <c r="CS58" s="1"/>
-      <c r="CT58" s="1"/>
-      <c r="CU58" s="2"/>
-      <c r="CV58" s="1"/>
-      <c r="CW58" s="2"/>
-      <c r="CX58" s="2"/>
-      <c r="CY58" s="2"/>
-      <c r="CZ58" s="1"/>
-      <c r="DA58" s="2"/>
-      <c r="DB58" s="1"/>
-    </row>
-    <row r="59" spans="11:106" x14ac:dyDescent="0.3">
-      <c r="AN59" s="3">
-        <v>7</v>
-      </c>
-      <c r="AO59" s="1"/>
-      <c r="AP59" s="1"/>
-      <c r="AQ59" s="2"/>
-      <c r="AR59" s="1"/>
-      <c r="AS59" s="2"/>
-      <c r="AT59" s="2"/>
-      <c r="AU59" s="2"/>
-      <c r="AV59" s="1"/>
-      <c r="AW59" s="2"/>
-      <c r="AX59" s="1"/>
+      <c r="CI58" s="140"/>
+      <c r="CJ58" s="140"/>
+      <c r="CK58" s="140"/>
+      <c r="CL58" s="140"/>
+      <c r="CM58" s="140"/>
+      <c r="CN58" s="140"/>
+      <c r="CO58" s="140"/>
+      <c r="CP58" s="140"/>
+      <c r="CQ58" s="140"/>
+      <c r="CR58" s="140"/>
+      <c r="CS58" s="140"/>
+      <c r="CT58" s="140"/>
+      <c r="CU58" s="140"/>
+      <c r="CV58" s="140"/>
+      <c r="CW58" s="140"/>
+      <c r="CX58" s="140"/>
+      <c r="CY58" s="140"/>
+      <c r="CZ58" s="140"/>
+      <c r="DA58" s="140"/>
+      <c r="DB58" s="140"/>
+      <c r="DC58" s="140"/>
+      <c r="DD58" s="140"/>
+      <c r="DE58" s="140"/>
+      <c r="DF58" s="140"/>
+      <c r="DG58" s="140"/>
+      <c r="DH58" s="140"/>
+      <c r="DI58" s="140"/>
+      <c r="DJ58" s="140"/>
+      <c r="DK58" s="140"/>
+      <c r="DL58" s="140"/>
+      <c r="DM58" s="140"/>
+      <c r="DN58" s="140"/>
+      <c r="DO58" s="140"/>
+      <c r="DP58" s="140"/>
+      <c r="DQ58" s="140"/>
+      <c r="DR58" s="140"/>
+      <c r="DS58" s="140"/>
+      <c r="DT58" s="140"/>
+      <c r="DU58" s="140"/>
+      <c r="DV58" s="140"/>
+      <c r="DW58" s="140"/>
+      <c r="DX58" s="140"/>
+      <c r="DY58" s="140"/>
+      <c r="DZ58" s="140"/>
+      <c r="EA58" s="140"/>
+      <c r="EB58" s="140"/>
+      <c r="EC58" s="140"/>
+      <c r="ED58" s="140"/>
+      <c r="EE58" s="140"/>
+      <c r="EF58" s="140"/>
+      <c r="EG58" s="140"/>
+      <c r="EH58" s="140"/>
+      <c r="EI58" s="140"/>
+      <c r="EJ58" s="140"/>
+      <c r="EK58" s="140"/>
+      <c r="EL58" s="140"/>
+      <c r="EM58" s="140"/>
+      <c r="EN58" s="140"/>
+      <c r="EO58" s="140"/>
+      <c r="EP58" s="140"/>
+      <c r="EQ58" s="140"/>
+      <c r="ER58" s="140"/>
+      <c r="ES58" s="140"/>
+      <c r="ET58" s="140"/>
+      <c r="EU58" s="140"/>
+      <c r="EV58" s="140"/>
+      <c r="EW58" s="140"/>
+      <c r="EX58" s="140"/>
+      <c r="EY58" s="140"/>
+      <c r="EZ58" s="140"/>
+      <c r="FA58" s="140"/>
+      <c r="FB58" s="140"/>
+      <c r="FC58" s="140"/>
+      <c r="FD58" s="140"/>
+      <c r="FE58" s="140"/>
+      <c r="FF58" s="140"/>
+      <c r="FG58" s="140"/>
+      <c r="FH58" s="140"/>
+      <c r="FI58" s="140"/>
+      <c r="FJ58" s="140"/>
+      <c r="FK58" s="140"/>
+      <c r="FL58" s="140"/>
+      <c r="FM58" s="140"/>
+      <c r="FN58" s="140"/>
+      <c r="FO58" s="140"/>
+      <c r="FP58" s="140"/>
+      <c r="FQ58" s="140"/>
+      <c r="FR58" s="140"/>
+      <c r="FS58" s="140"/>
+      <c r="FT58" s="140"/>
+      <c r="FU58" s="140"/>
+      <c r="FV58" s="140"/>
+      <c r="FW58" s="140"/>
+      <c r="FX58" s="140"/>
+    </row>
+    <row r="59" spans="11:180" x14ac:dyDescent="0.3">
       <c r="BQ59" s="3">
         <v>6</v>
       </c>
@@ -14109,28 +15530,102 @@
       <c r="BY59" s="2"/>
       <c r="BZ59" s="1"/>
       <c r="CA59" s="1"/>
-      <c r="CI59" s="1"/>
-      <c r="CJ59" s="1"/>
-      <c r="CK59" s="1"/>
-      <c r="CL59" s="2"/>
-      <c r="CM59" s="1"/>
-      <c r="CN59" s="2"/>
-      <c r="CO59" s="1"/>
-      <c r="CP59" s="2"/>
-      <c r="CQ59" s="1"/>
-      <c r="CR59" s="1"/>
-      <c r="CS59" s="1"/>
-      <c r="CT59" s="1"/>
-      <c r="CU59" s="1"/>
-      <c r="CV59" s="2"/>
-      <c r="CW59" s="1"/>
-      <c r="CX59" s="2"/>
-      <c r="CY59" s="1"/>
-      <c r="CZ59" s="2"/>
-      <c r="DA59" s="1"/>
-      <c r="DB59" s="1"/>
-    </row>
-    <row r="60" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI59" s="140"/>
+      <c r="CJ59" s="140"/>
+      <c r="CK59" s="140"/>
+      <c r="CL59" s="140"/>
+      <c r="CM59" s="140"/>
+      <c r="CN59" s="140"/>
+      <c r="CO59" s="140"/>
+      <c r="CP59" s="140"/>
+      <c r="CQ59" s="140"/>
+      <c r="CR59" s="140"/>
+      <c r="CS59" s="140"/>
+      <c r="CT59" s="140"/>
+      <c r="CU59" s="140"/>
+      <c r="CV59" s="140"/>
+      <c r="CW59" s="140"/>
+      <c r="CX59" s="140"/>
+      <c r="CY59" s="140"/>
+      <c r="CZ59" s="140"/>
+      <c r="DA59" s="140"/>
+      <c r="DB59" s="140"/>
+      <c r="DC59" s="140"/>
+      <c r="DD59" s="140"/>
+      <c r="DE59" s="140"/>
+      <c r="DF59" s="140"/>
+      <c r="DG59" s="140"/>
+      <c r="DH59" s="140"/>
+      <c r="DI59" s="140"/>
+      <c r="DJ59" s="140"/>
+      <c r="DK59" s="140"/>
+      <c r="DL59" s="140"/>
+      <c r="DM59" s="140"/>
+      <c r="DN59" s="140"/>
+      <c r="DO59" s="140"/>
+      <c r="DP59" s="140"/>
+      <c r="DQ59" s="140"/>
+      <c r="DR59" s="140"/>
+      <c r="DS59" s="140"/>
+      <c r="DT59" s="140"/>
+      <c r="DU59" s="140"/>
+      <c r="DV59" s="140"/>
+      <c r="DW59" s="140"/>
+      <c r="DX59" s="140"/>
+      <c r="DY59" s="140"/>
+      <c r="DZ59" s="140"/>
+      <c r="EA59" s="140"/>
+      <c r="EB59" s="140"/>
+      <c r="EC59" s="140"/>
+      <c r="ED59" s="140"/>
+      <c r="EE59" s="140"/>
+      <c r="EF59" s="140"/>
+      <c r="EG59" s="140"/>
+      <c r="EH59" s="140"/>
+      <c r="EI59" s="140"/>
+      <c r="EJ59" s="140"/>
+      <c r="EK59" s="140"/>
+      <c r="EL59" s="140"/>
+      <c r="EM59" s="140"/>
+      <c r="EN59" s="140"/>
+      <c r="EO59" s="140"/>
+      <c r="EP59" s="140"/>
+      <c r="EQ59" s="140"/>
+      <c r="ER59" s="140"/>
+      <c r="ES59" s="140"/>
+      <c r="ET59" s="140"/>
+      <c r="EU59" s="140"/>
+      <c r="EV59" s="140"/>
+      <c r="EW59" s="140"/>
+      <c r="EX59" s="140"/>
+      <c r="EY59" s="140"/>
+      <c r="EZ59" s="140"/>
+      <c r="FA59" s="140"/>
+      <c r="FB59" s="140"/>
+      <c r="FC59" s="140"/>
+      <c r="FD59" s="140"/>
+      <c r="FE59" s="140"/>
+      <c r="FF59" s="140"/>
+      <c r="FG59" s="140"/>
+      <c r="FH59" s="140"/>
+      <c r="FI59" s="140"/>
+      <c r="FJ59" s="140"/>
+      <c r="FK59" s="140"/>
+      <c r="FL59" s="140"/>
+      <c r="FM59" s="140"/>
+      <c r="FN59" s="140"/>
+      <c r="FO59" s="140"/>
+      <c r="FP59" s="140"/>
+      <c r="FQ59" s="140"/>
+      <c r="FR59" s="140"/>
+      <c r="FS59" s="140"/>
+      <c r="FT59" s="140"/>
+      <c r="FU59" s="140"/>
+      <c r="FV59" s="140"/>
+      <c r="FW59" s="140"/>
+      <c r="FX59" s="140"/>
+    </row>
+    <row r="60" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K60" s="3">
         <v>6</v>
       </c>
@@ -14149,19 +15644,6 @@
       <c r="AB60" s="2"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="2"/>
-      <c r="AN60" s="3">
-        <v>6</v>
-      </c>
-      <c r="AO60" s="1"/>
-      <c r="AP60" s="1"/>
-      <c r="AQ60" s="1"/>
-      <c r="AR60" s="2"/>
-      <c r="AS60" s="1"/>
-      <c r="AT60" s="2"/>
-      <c r="AU60" s="1"/>
-      <c r="AV60" s="2"/>
-      <c r="AW60" s="1"/>
-      <c r="AX60" s="1"/>
       <c r="BQ60" s="3">
         <v>5</v>
       </c>
@@ -14175,28 +15657,102 @@
       <c r="BY60" s="1"/>
       <c r="BZ60" s="1"/>
       <c r="CA60" s="1"/>
-      <c r="CI60" s="1"/>
-      <c r="CJ60" s="1"/>
-      <c r="CK60" s="1"/>
-      <c r="CL60" s="1"/>
-      <c r="CM60" s="2"/>
-      <c r="CN60" s="1"/>
-      <c r="CO60" s="2"/>
-      <c r="CP60" s="1"/>
-      <c r="CQ60" s="1"/>
-      <c r="CR60" s="1"/>
-      <c r="CS60" s="1"/>
-      <c r="CT60" s="1"/>
-      <c r="CU60" s="1"/>
-      <c r="CV60" s="1"/>
-      <c r="CW60" s="2"/>
-      <c r="CX60" s="1"/>
-      <c r="CY60" s="2"/>
-      <c r="CZ60" s="1"/>
-      <c r="DA60" s="1"/>
-      <c r="DB60" s="1"/>
-    </row>
-    <row r="61" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI60" s="140"/>
+      <c r="CJ60" s="140"/>
+      <c r="CK60" s="140"/>
+      <c r="CL60" s="140"/>
+      <c r="CM60" s="140"/>
+      <c r="CN60" s="140"/>
+      <c r="CO60" s="140"/>
+      <c r="CP60" s="140"/>
+      <c r="CQ60" s="140"/>
+      <c r="CR60" s="140"/>
+      <c r="CS60" s="140"/>
+      <c r="CT60" s="140"/>
+      <c r="CU60" s="140"/>
+      <c r="CV60" s="140"/>
+      <c r="CW60" s="140"/>
+      <c r="CX60" s="140"/>
+      <c r="CY60" s="140"/>
+      <c r="CZ60" s="140"/>
+      <c r="DA60" s="140"/>
+      <c r="DB60" s="140"/>
+      <c r="DC60" s="140"/>
+      <c r="DD60" s="140"/>
+      <c r="DE60" s="140"/>
+      <c r="DF60" s="140"/>
+      <c r="DG60" s="140"/>
+      <c r="DH60" s="140"/>
+      <c r="DI60" s="140"/>
+      <c r="DJ60" s="140"/>
+      <c r="DK60" s="140"/>
+      <c r="DL60" s="140"/>
+      <c r="DM60" s="140"/>
+      <c r="DN60" s="140"/>
+      <c r="DO60" s="140"/>
+      <c r="DP60" s="140"/>
+      <c r="DQ60" s="140"/>
+      <c r="DR60" s="140"/>
+      <c r="DS60" s="140"/>
+      <c r="DT60" s="140"/>
+      <c r="DU60" s="140"/>
+      <c r="DV60" s="140"/>
+      <c r="DW60" s="140"/>
+      <c r="DX60" s="140"/>
+      <c r="DY60" s="140"/>
+      <c r="DZ60" s="140"/>
+      <c r="EA60" s="140"/>
+      <c r="EB60" s="140"/>
+      <c r="EC60" s="140"/>
+      <c r="ED60" s="140"/>
+      <c r="EE60" s="140"/>
+      <c r="EF60" s="140"/>
+      <c r="EG60" s="140"/>
+      <c r="EH60" s="140"/>
+      <c r="EI60" s="140"/>
+      <c r="EJ60" s="140"/>
+      <c r="EK60" s="140"/>
+      <c r="EL60" s="140"/>
+      <c r="EM60" s="140"/>
+      <c r="EN60" s="140"/>
+      <c r="EO60" s="140"/>
+      <c r="EP60" s="140"/>
+      <c r="EQ60" s="140"/>
+      <c r="ER60" s="140"/>
+      <c r="ES60" s="140"/>
+      <c r="ET60" s="140"/>
+      <c r="EU60" s="140"/>
+      <c r="EV60" s="140"/>
+      <c r="EW60" s="140"/>
+      <c r="EX60" s="140"/>
+      <c r="EY60" s="140"/>
+      <c r="EZ60" s="140"/>
+      <c r="FA60" s="140"/>
+      <c r="FB60" s="140"/>
+      <c r="FC60" s="140"/>
+      <c r="FD60" s="140"/>
+      <c r="FE60" s="140"/>
+      <c r="FF60" s="140"/>
+      <c r="FG60" s="140"/>
+      <c r="FH60" s="140"/>
+      <c r="FI60" s="140"/>
+      <c r="FJ60" s="140"/>
+      <c r="FK60" s="140"/>
+      <c r="FL60" s="140"/>
+      <c r="FM60" s="140"/>
+      <c r="FN60" s="140"/>
+      <c r="FO60" s="140"/>
+      <c r="FP60" s="140"/>
+      <c r="FQ60" s="140"/>
+      <c r="FR60" s="140"/>
+      <c r="FS60" s="140"/>
+      <c r="FT60" s="140"/>
+      <c r="FU60" s="140"/>
+      <c r="FV60" s="140"/>
+      <c r="FW60" s="140"/>
+      <c r="FX60" s="140"/>
+    </row>
+    <row r="61" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K61" s="3">
         <v>5</v>
       </c>
@@ -14215,19 +15771,6 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="2"/>
       <c r="AD61" s="1"/>
-      <c r="AN61" s="3">
-        <v>5</v>
-      </c>
-      <c r="AO61" s="1"/>
-      <c r="AP61" s="1"/>
-      <c r="AQ61" s="1"/>
-      <c r="AR61" s="1"/>
-      <c r="AS61" s="2"/>
-      <c r="AT61" s="1"/>
-      <c r="AU61" s="2"/>
-      <c r="AV61" s="1"/>
-      <c r="AW61" s="1"/>
-      <c r="AX61" s="1"/>
       <c r="BQ61" s="3">
         <v>4</v>
       </c>
@@ -14241,28 +15784,102 @@
       <c r="BY61" s="2"/>
       <c r="BZ61" s="1"/>
       <c r="CA61" s="1"/>
-      <c r="CI61" s="1"/>
-      <c r="CJ61" s="1"/>
-      <c r="CK61" s="1"/>
-      <c r="CL61" s="2"/>
-      <c r="CM61" s="1"/>
-      <c r="CN61" s="2"/>
-      <c r="CO61" s="1"/>
-      <c r="CP61" s="2"/>
-      <c r="CQ61" s="1"/>
-      <c r="CR61" s="1"/>
-      <c r="CS61" s="1"/>
-      <c r="CT61" s="1"/>
-      <c r="CU61" s="1"/>
-      <c r="CV61" s="2"/>
-      <c r="CW61" s="1"/>
-      <c r="CX61" s="2"/>
-      <c r="CY61" s="1"/>
-      <c r="CZ61" s="2"/>
-      <c r="DA61" s="1"/>
-      <c r="DB61" s="1"/>
-    </row>
-    <row r="62" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI61" s="140"/>
+      <c r="CJ61" s="140"/>
+      <c r="CK61" s="140"/>
+      <c r="CL61" s="140"/>
+      <c r="CM61" s="140"/>
+      <c r="CN61" s="140"/>
+      <c r="CO61" s="140"/>
+      <c r="CP61" s="140"/>
+      <c r="CQ61" s="140"/>
+      <c r="CR61" s="140"/>
+      <c r="CS61" s="140"/>
+      <c r="CT61" s="140"/>
+      <c r="CU61" s="140"/>
+      <c r="CV61" s="140"/>
+      <c r="CW61" s="140"/>
+      <c r="CX61" s="140"/>
+      <c r="CY61" s="140"/>
+      <c r="CZ61" s="140"/>
+      <c r="DA61" s="140"/>
+      <c r="DB61" s="140"/>
+      <c r="DC61" s="140"/>
+      <c r="DD61" s="140"/>
+      <c r="DE61" s="140"/>
+      <c r="DF61" s="140"/>
+      <c r="DG61" s="140"/>
+      <c r="DH61" s="140"/>
+      <c r="DI61" s="140"/>
+      <c r="DJ61" s="140"/>
+      <c r="DK61" s="140"/>
+      <c r="DL61" s="140"/>
+      <c r="DM61" s="140"/>
+      <c r="DN61" s="140"/>
+      <c r="DO61" s="140"/>
+      <c r="DP61" s="140"/>
+      <c r="DQ61" s="140"/>
+      <c r="DR61" s="140"/>
+      <c r="DS61" s="140"/>
+      <c r="DT61" s="140"/>
+      <c r="DU61" s="140"/>
+      <c r="DV61" s="140"/>
+      <c r="DW61" s="140"/>
+      <c r="DX61" s="140"/>
+      <c r="DY61" s="140"/>
+      <c r="DZ61" s="140"/>
+      <c r="EA61" s="140"/>
+      <c r="EB61" s="140"/>
+      <c r="EC61" s="140"/>
+      <c r="ED61" s="140"/>
+      <c r="EE61" s="140"/>
+      <c r="EF61" s="140"/>
+      <c r="EG61" s="140"/>
+      <c r="EH61" s="140"/>
+      <c r="EI61" s="140"/>
+      <c r="EJ61" s="140"/>
+      <c r="EK61" s="140"/>
+      <c r="EL61" s="140"/>
+      <c r="EM61" s="140"/>
+      <c r="EN61" s="140"/>
+      <c r="EO61" s="140"/>
+      <c r="EP61" s="140"/>
+      <c r="EQ61" s="140"/>
+      <c r="ER61" s="140"/>
+      <c r="ES61" s="140"/>
+      <c r="ET61" s="140"/>
+      <c r="EU61" s="140"/>
+      <c r="EV61" s="140"/>
+      <c r="EW61" s="140"/>
+      <c r="EX61" s="140"/>
+      <c r="EY61" s="140"/>
+      <c r="EZ61" s="140"/>
+      <c r="FA61" s="140"/>
+      <c r="FB61" s="140"/>
+      <c r="FC61" s="140"/>
+      <c r="FD61" s="140"/>
+      <c r="FE61" s="140"/>
+      <c r="FF61" s="140"/>
+      <c r="FG61" s="140"/>
+      <c r="FH61" s="140"/>
+      <c r="FI61" s="140"/>
+      <c r="FJ61" s="140"/>
+      <c r="FK61" s="140"/>
+      <c r="FL61" s="140"/>
+      <c r="FM61" s="140"/>
+      <c r="FN61" s="140"/>
+      <c r="FO61" s="140"/>
+      <c r="FP61" s="140"/>
+      <c r="FQ61" s="140"/>
+      <c r="FR61" s="140"/>
+      <c r="FS61" s="140"/>
+      <c r="FT61" s="140"/>
+      <c r="FU61" s="140"/>
+      <c r="FV61" s="140"/>
+      <c r="FW61" s="140"/>
+      <c r="FX61" s="140"/>
+    </row>
+    <row r="62" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K62" s="3">
         <v>4</v>
       </c>
@@ -14281,19 +15898,6 @@
       <c r="AB62" s="2"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
-      <c r="AN62" s="3">
-        <v>4</v>
-      </c>
-      <c r="AO62" s="1"/>
-      <c r="AP62" s="1"/>
-      <c r="AQ62" s="1"/>
-      <c r="AR62" s="2"/>
-      <c r="AS62" s="1"/>
-      <c r="AT62" s="2"/>
-      <c r="AU62" s="1"/>
-      <c r="AV62" s="2"/>
-      <c r="AW62" s="1"/>
-      <c r="AX62" s="1"/>
       <c r="BQ62" s="3">
         <v>3</v>
       </c>
@@ -14307,28 +15911,102 @@
       <c r="BY62" s="1"/>
       <c r="BZ62" s="2"/>
       <c r="CA62" s="1"/>
-      <c r="CI62" s="1"/>
-      <c r="CJ62" s="1"/>
-      <c r="CK62" s="2"/>
-      <c r="CL62" s="1"/>
-      <c r="CM62" s="2"/>
-      <c r="CN62" s="2"/>
-      <c r="CO62" s="2"/>
-      <c r="CP62" s="1"/>
-      <c r="CQ62" s="2"/>
-      <c r="CR62" s="1"/>
-      <c r="CS62" s="1"/>
-      <c r="CT62" s="1"/>
-      <c r="CU62" s="2"/>
-      <c r="CV62" s="1"/>
-      <c r="CW62" s="2"/>
-      <c r="CX62" s="2"/>
-      <c r="CY62" s="2"/>
-      <c r="CZ62" s="1"/>
-      <c r="DA62" s="2"/>
-      <c r="DB62" s="1"/>
-    </row>
-    <row r="63" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI62" s="140"/>
+      <c r="CJ62" s="140"/>
+      <c r="CK62" s="140"/>
+      <c r="CL62" s="140"/>
+      <c r="CM62" s="140"/>
+      <c r="CN62" s="140"/>
+      <c r="CO62" s="140"/>
+      <c r="CP62" s="140"/>
+      <c r="CQ62" s="140"/>
+      <c r="CR62" s="140"/>
+      <c r="CS62" s="140"/>
+      <c r="CT62" s="140"/>
+      <c r="CU62" s="140"/>
+      <c r="CV62" s="140"/>
+      <c r="CW62" s="140"/>
+      <c r="CX62" s="140"/>
+      <c r="CY62" s="140"/>
+      <c r="CZ62" s="140"/>
+      <c r="DA62" s="140"/>
+      <c r="DB62" s="140"/>
+      <c r="DC62" s="140"/>
+      <c r="DD62" s="140"/>
+      <c r="DE62" s="140"/>
+      <c r="DF62" s="140"/>
+      <c r="DG62" s="140"/>
+      <c r="DH62" s="140"/>
+      <c r="DI62" s="140"/>
+      <c r="DJ62" s="140"/>
+      <c r="DK62" s="140"/>
+      <c r="DL62" s="140"/>
+      <c r="DM62" s="140"/>
+      <c r="DN62" s="140"/>
+      <c r="DO62" s="140"/>
+      <c r="DP62" s="140"/>
+      <c r="DQ62" s="140"/>
+      <c r="DR62" s="140"/>
+      <c r="DS62" s="140"/>
+      <c r="DT62" s="140"/>
+      <c r="DU62" s="140"/>
+      <c r="DV62" s="140"/>
+      <c r="DW62" s="140"/>
+      <c r="DX62" s="140"/>
+      <c r="DY62" s="140"/>
+      <c r="DZ62" s="140"/>
+      <c r="EA62" s="140"/>
+      <c r="EB62" s="140"/>
+      <c r="EC62" s="140"/>
+      <c r="ED62" s="140"/>
+      <c r="EE62" s="140"/>
+      <c r="EF62" s="140"/>
+      <c r="EG62" s="140"/>
+      <c r="EH62" s="140"/>
+      <c r="EI62" s="140"/>
+      <c r="EJ62" s="140"/>
+      <c r="EK62" s="140"/>
+      <c r="EL62" s="140"/>
+      <c r="EM62" s="140"/>
+      <c r="EN62" s="140"/>
+      <c r="EO62" s="140"/>
+      <c r="EP62" s="140"/>
+      <c r="EQ62" s="140"/>
+      <c r="ER62" s="140"/>
+      <c r="ES62" s="140"/>
+      <c r="ET62" s="140"/>
+      <c r="EU62" s="140"/>
+      <c r="EV62" s="140"/>
+      <c r="EW62" s="140"/>
+      <c r="EX62" s="140"/>
+      <c r="EY62" s="140"/>
+      <c r="EZ62" s="140"/>
+      <c r="FA62" s="140"/>
+      <c r="FB62" s="140"/>
+      <c r="FC62" s="140"/>
+      <c r="FD62" s="140"/>
+      <c r="FE62" s="140"/>
+      <c r="FF62" s="140"/>
+      <c r="FG62" s="140"/>
+      <c r="FH62" s="140"/>
+      <c r="FI62" s="140"/>
+      <c r="FJ62" s="140"/>
+      <c r="FK62" s="140"/>
+      <c r="FL62" s="140"/>
+      <c r="FM62" s="140"/>
+      <c r="FN62" s="140"/>
+      <c r="FO62" s="140"/>
+      <c r="FP62" s="140"/>
+      <c r="FQ62" s="140"/>
+      <c r="FR62" s="140"/>
+      <c r="FS62" s="140"/>
+      <c r="FT62" s="140"/>
+      <c r="FU62" s="140"/>
+      <c r="FV62" s="140"/>
+      <c r="FW62" s="140"/>
+      <c r="FX62" s="140"/>
+    </row>
+    <row r="63" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K63" s="3">
         <v>3</v>
       </c>
@@ -14347,19 +16025,6 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
-      <c r="AN63" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO63" s="1"/>
-      <c r="AP63" s="1"/>
-      <c r="AQ63" s="2"/>
-      <c r="AR63" s="1"/>
-      <c r="AS63" s="2"/>
-      <c r="AT63" s="2"/>
-      <c r="AU63" s="2"/>
-      <c r="AV63" s="1"/>
-      <c r="AW63" s="2"/>
-      <c r="AX63" s="1"/>
       <c r="BQ63" s="3">
         <v>2</v>
       </c>
@@ -14373,28 +16038,102 @@
       <c r="BY63" s="2"/>
       <c r="BZ63" s="1"/>
       <c r="CA63" s="2"/>
-      <c r="CI63" s="1"/>
-      <c r="CJ63" s="2"/>
-      <c r="CK63" s="1"/>
-      <c r="CL63" s="2"/>
-      <c r="CM63" s="2"/>
-      <c r="CN63" s="2"/>
-      <c r="CO63" s="2"/>
-      <c r="CP63" s="2"/>
-      <c r="CQ63" s="1"/>
-      <c r="CR63" s="2"/>
-      <c r="CS63" s="1"/>
-      <c r="CT63" s="2"/>
-      <c r="CU63" s="1"/>
-      <c r="CV63" s="2"/>
-      <c r="CW63" s="2"/>
-      <c r="CX63" s="2"/>
-      <c r="CY63" s="2"/>
-      <c r="CZ63" s="2"/>
-      <c r="DA63" s="1"/>
-      <c r="DB63" s="2"/>
-    </row>
-    <row r="64" spans="11:106" x14ac:dyDescent="0.3">
+      <c r="CI63" s="140"/>
+      <c r="CJ63" s="140"/>
+      <c r="CK63" s="140"/>
+      <c r="CL63" s="140"/>
+      <c r="CM63" s="140"/>
+      <c r="CN63" s="140"/>
+      <c r="CO63" s="140"/>
+      <c r="CP63" s="140"/>
+      <c r="CQ63" s="140"/>
+      <c r="CR63" s="140"/>
+      <c r="CS63" s="140"/>
+      <c r="CT63" s="140"/>
+      <c r="CU63" s="140"/>
+      <c r="CV63" s="140"/>
+      <c r="CW63" s="140"/>
+      <c r="CX63" s="140"/>
+      <c r="CY63" s="140"/>
+      <c r="CZ63" s="140"/>
+      <c r="DA63" s="140"/>
+      <c r="DB63" s="140"/>
+      <c r="DC63" s="140"/>
+      <c r="DD63" s="140"/>
+      <c r="DE63" s="140"/>
+      <c r="DF63" s="140"/>
+      <c r="DG63" s="140"/>
+      <c r="DH63" s="140"/>
+      <c r="DI63" s="140"/>
+      <c r="DJ63" s="140"/>
+      <c r="DK63" s="140"/>
+      <c r="DL63" s="140"/>
+      <c r="DM63" s="140"/>
+      <c r="DN63" s="140"/>
+      <c r="DO63" s="140"/>
+      <c r="DP63" s="140"/>
+      <c r="DQ63" s="140"/>
+      <c r="DR63" s="140"/>
+      <c r="DS63" s="140"/>
+      <c r="DT63" s="140"/>
+      <c r="DU63" s="140"/>
+      <c r="DV63" s="140"/>
+      <c r="DW63" s="140"/>
+      <c r="DX63" s="140"/>
+      <c r="DY63" s="140"/>
+      <c r="DZ63" s="140"/>
+      <c r="EA63" s="140"/>
+      <c r="EB63" s="140"/>
+      <c r="EC63" s="140"/>
+      <c r="ED63" s="140"/>
+      <c r="EE63" s="140"/>
+      <c r="EF63" s="140"/>
+      <c r="EG63" s="140"/>
+      <c r="EH63" s="140"/>
+      <c r="EI63" s="140"/>
+      <c r="EJ63" s="140"/>
+      <c r="EK63" s="140"/>
+      <c r="EL63" s="140"/>
+      <c r="EM63" s="140"/>
+      <c r="EN63" s="140"/>
+      <c r="EO63" s="140"/>
+      <c r="EP63" s="140"/>
+      <c r="EQ63" s="140"/>
+      <c r="ER63" s="140"/>
+      <c r="ES63" s="140"/>
+      <c r="ET63" s="140"/>
+      <c r="EU63" s="140"/>
+      <c r="EV63" s="140"/>
+      <c r="EW63" s="140"/>
+      <c r="EX63" s="140"/>
+      <c r="EY63" s="140"/>
+      <c r="EZ63" s="140"/>
+      <c r="FA63" s="140"/>
+      <c r="FB63" s="140"/>
+      <c r="FC63" s="140"/>
+      <c r="FD63" s="140"/>
+      <c r="FE63" s="140"/>
+      <c r="FF63" s="140"/>
+      <c r="FG63" s="140"/>
+      <c r="FH63" s="140"/>
+      <c r="FI63" s="140"/>
+      <c r="FJ63" s="140"/>
+      <c r="FK63" s="140"/>
+      <c r="FL63" s="140"/>
+      <c r="FM63" s="140"/>
+      <c r="FN63" s="140"/>
+      <c r="FO63" s="140"/>
+      <c r="FP63" s="140"/>
+      <c r="FQ63" s="140"/>
+      <c r="FR63" s="140"/>
+      <c r="FS63" s="140"/>
+      <c r="FT63" s="140"/>
+      <c r="FU63" s="140"/>
+      <c r="FV63" s="140"/>
+      <c r="FW63" s="140"/>
+      <c r="FX63" s="140"/>
+    </row>
+    <row r="64" spans="11:180" x14ac:dyDescent="0.3">
       <c r="K64" s="3">
         <v>2</v>
       </c>
@@ -14413,19 +16152,6 @@
       <c r="AB64" s="2"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
-      <c r="AN64" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO64" s="1"/>
-      <c r="AP64" s="2"/>
-      <c r="AQ64" s="1"/>
-      <c r="AR64" s="2"/>
-      <c r="AS64" s="2"/>
-      <c r="AT64" s="2"/>
-      <c r="AU64" s="2"/>
-      <c r="AV64" s="2"/>
-      <c r="AW64" s="1"/>
-      <c r="AX64" s="2"/>
       <c r="BQ64" s="3">
         <v>1</v>
       </c>
@@ -14439,26 +16165,100 @@
       <c r="BY64" s="2"/>
       <c r="BZ64" s="2"/>
       <c r="CA64" s="1"/>
-      <c r="CI64" s="2"/>
-      <c r="CJ64" s="1"/>
-      <c r="CK64" s="2"/>
-      <c r="CL64" s="2"/>
-      <c r="CM64" s="2"/>
-      <c r="CN64" s="2"/>
-      <c r="CO64" s="2"/>
-      <c r="CP64" s="2"/>
-      <c r="CQ64" s="2"/>
-      <c r="CR64" s="1"/>
-      <c r="CS64" s="2"/>
-      <c r="CT64" s="1"/>
-      <c r="CU64" s="2"/>
-      <c r="CV64" s="2"/>
-      <c r="CW64" s="2"/>
-      <c r="CX64" s="2"/>
-      <c r="CY64" s="2"/>
-      <c r="CZ64" s="2"/>
-      <c r="DA64" s="2"/>
-      <c r="DB64" s="1"/>
+      <c r="CI64" s="140"/>
+      <c r="CJ64" s="140"/>
+      <c r="CK64" s="140"/>
+      <c r="CL64" s="140"/>
+      <c r="CM64" s="140"/>
+      <c r="CN64" s="140"/>
+      <c r="CO64" s="140"/>
+      <c r="CP64" s="140"/>
+      <c r="CQ64" s="140"/>
+      <c r="CR64" s="140"/>
+      <c r="CS64" s="140"/>
+      <c r="CT64" s="140"/>
+      <c r="CU64" s="140"/>
+      <c r="CV64" s="140"/>
+      <c r="CW64" s="140"/>
+      <c r="CX64" s="140"/>
+      <c r="CY64" s="140"/>
+      <c r="CZ64" s="140"/>
+      <c r="DA64" s="140"/>
+      <c r="DB64" s="140"/>
+      <c r="DC64" s="140"/>
+      <c r="DD64" s="140"/>
+      <c r="DE64" s="140"/>
+      <c r="DF64" s="140"/>
+      <c r="DG64" s="140"/>
+      <c r="DH64" s="140"/>
+      <c r="DI64" s="140"/>
+      <c r="DJ64" s="140"/>
+      <c r="DK64" s="140"/>
+      <c r="DL64" s="140"/>
+      <c r="DM64" s="140"/>
+      <c r="DN64" s="140"/>
+      <c r="DO64" s="140"/>
+      <c r="DP64" s="140"/>
+      <c r="DQ64" s="140"/>
+      <c r="DR64" s="140"/>
+      <c r="DS64" s="140"/>
+      <c r="DT64" s="140"/>
+      <c r="DU64" s="140"/>
+      <c r="DV64" s="140"/>
+      <c r="DW64" s="140"/>
+      <c r="DX64" s="140"/>
+      <c r="DY64" s="140"/>
+      <c r="DZ64" s="140"/>
+      <c r="EA64" s="140"/>
+      <c r="EB64" s="140"/>
+      <c r="EC64" s="140"/>
+      <c r="ED64" s="140"/>
+      <c r="EE64" s="140"/>
+      <c r="EF64" s="140"/>
+      <c r="EG64" s="140"/>
+      <c r="EH64" s="140"/>
+      <c r="EI64" s="140"/>
+      <c r="EJ64" s="140"/>
+      <c r="EK64" s="140"/>
+      <c r="EL64" s="140"/>
+      <c r="EM64" s="140"/>
+      <c r="EN64" s="140"/>
+      <c r="EO64" s="140"/>
+      <c r="EP64" s="140"/>
+      <c r="EQ64" s="140"/>
+      <c r="ER64" s="140"/>
+      <c r="ES64" s="140"/>
+      <c r="ET64" s="140"/>
+      <c r="EU64" s="140"/>
+      <c r="EV64" s="140"/>
+      <c r="EW64" s="140"/>
+      <c r="EX64" s="140"/>
+      <c r="EY64" s="140"/>
+      <c r="EZ64" s="140"/>
+      <c r="FA64" s="140"/>
+      <c r="FB64" s="140"/>
+      <c r="FC64" s="140"/>
+      <c r="FD64" s="140"/>
+      <c r="FE64" s="140"/>
+      <c r="FF64" s="140"/>
+      <c r="FG64" s="140"/>
+      <c r="FH64" s="140"/>
+      <c r="FI64" s="140"/>
+      <c r="FJ64" s="140"/>
+      <c r="FK64" s="140"/>
+      <c r="FL64" s="140"/>
+      <c r="FM64" s="140"/>
+      <c r="FN64" s="140"/>
+      <c r="FO64" s="140"/>
+      <c r="FP64" s="140"/>
+      <c r="FQ64" s="140"/>
+      <c r="FR64" s="140"/>
+      <c r="FS64" s="140"/>
+      <c r="FT64" s="140"/>
+      <c r="FU64" s="140"/>
+      <c r="FV64" s="140"/>
+      <c r="FW64" s="140"/>
+      <c r="FX64" s="140"/>
     </row>
     <row r="65" spans="11:98" x14ac:dyDescent="0.3">
       <c r="K65" s="3">
@@ -14479,19 +16279,6 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="2"/>
       <c r="AD65" s="1"/>
-      <c r="AN65" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO65" s="2"/>
-      <c r="AP65" s="1"/>
-      <c r="AQ65" s="2"/>
-      <c r="AR65" s="2"/>
-      <c r="AS65" s="2"/>
-      <c r="AT65" s="2"/>
-      <c r="AU65" s="2"/>
-      <c r="AV65" s="2"/>
-      <c r="AW65" s="2"/>
-      <c r="AX65" s="1"/>
       <c r="BQ65" s="3" t="s">
         <v>0</v>
       </c>
@@ -14568,39 +16355,6 @@
       </c>
       <c r="AD66" s="3">
         <v>6</v>
-      </c>
-      <c r="AN66" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO66" s="3">
-        <v>1</v>
-      </c>
-      <c r="AP66" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ66" s="3">
-        <v>3</v>
-      </c>
-      <c r="AR66" s="3">
-        <v>4</v>
-      </c>
-      <c r="AS66" s="3">
-        <v>5</v>
-      </c>
-      <c r="AT66" s="3">
-        <v>6</v>
-      </c>
-      <c r="AU66" s="3">
-        <v>7</v>
-      </c>
-      <c r="AV66" s="3">
-        <v>8</v>
-      </c>
-      <c r="AW66" s="3">
-        <v>9</v>
-      </c>
-      <c r="AX66" s="3">
-        <v>10</v>
       </c>
     </row>
     <row r="69" spans="11:98" x14ac:dyDescent="0.3">
@@ -17782,6 +19536,127 @@
       <c r="AN124" s="2"/>
       <c r="AO124" s="2"/>
     </row>
+    <row r="138" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF138" s="124"/>
+      <c r="AH138" s="126"/>
+    </row>
+    <row r="139" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF139" s="124"/>
+      <c r="AH139" s="126"/>
+    </row>
+    <row r="140" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF140" s="123"/>
+      <c r="AH140" s="123"/>
+    </row>
+    <row r="141" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF141" s="123"/>
+      <c r="AH141" s="123"/>
+    </row>
+    <row r="142" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF142" s="123"/>
+      <c r="AH142" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF143" s="124"/>
+      <c r="AH143" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF144" s="124"/>
+      <c r="AH144" s="126"/>
+    </row>
+    <row r="145" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="X145" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF145" s="123"/>
+      <c r="AH145" s="125"/>
+    </row>
+    <row r="146" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="X146" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF146" s="124"/>
+      <c r="AH146" s="126"/>
+    </row>
+    <row r="147" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF147" s="124"/>
+      <c r="AH147" s="126"/>
+    </row>
+    <row r="148" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="X148" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF148" s="123"/>
+      <c r="AH148" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF149" s="123"/>
+      <c r="AH149" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF150" s="123"/>
+      <c r="AH150" s="123"/>
+    </row>
+    <row r="151" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF151" s="124"/>
+      <c r="AH151" s="124"/>
+    </row>
+    <row r="152" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF152" s="124"/>
+      <c r="AH152" s="124"/>
+    </row>
+    <row r="153" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF153" s="123"/>
+      <c r="AH153" s="123"/>
+    </row>
+    <row r="154" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF154" s="124"/>
+      <c r="AH154" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF155" s="124"/>
+      <c r="AH155" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF156" s="123"/>
+      <c r="AH156" s="125"/>
+    </row>
+    <row r="157" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF157" s="123"/>
+      <c r="AH157" s="125"/>
+    </row>
+    <row r="158" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF158" s="123"/>
+      <c r="AH158" s="125"/>
+    </row>
+    <row r="159" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF159" s="124"/>
+      <c r="AH159" s="124"/>
+    </row>
+    <row r="160" spans="24:34" x14ac:dyDescent="0.3">
+      <c r="AF160" s="124"/>
+      <c r="AH160" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" spans="32:34" x14ac:dyDescent="0.3">
+      <c r="AF161" s="123"/>
+      <c r="AH161" s="121" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -25935,14 +27810,14 @@
       <c r="BW14" s="68"/>
     </row>
     <row r="15" spans="4:75" x14ac:dyDescent="0.5">
-      <c r="H15" s="115" t="s">
+      <c r="H15" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="115"/>
-      <c r="M15" s="115"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="128"/>
+      <c r="M15" s="128"/>
       <c r="BV15" s="68"/>
       <c r="BW15" s="68"/>
     </row>
@@ -26506,16 +28381,16 @@
       <c r="BW34" s="68"/>
     </row>
     <row r="35" spans="4:77" x14ac:dyDescent="0.5">
-      <c r="J35" s="115" t="s">
+      <c r="J35" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="K35" s="115"/>
-      <c r="L35" s="115"/>
-      <c r="M35" s="115"/>
-      <c r="N35" s="115"/>
-      <c r="O35" s="115"/>
-      <c r="P35" s="115"/>
-      <c r="Q35" s="115"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -27215,28 +29090,28 @@
       <c r="W49" s="68"/>
       <c r="X49" s="68"/>
       <c r="Y49" s="68"/>
-      <c r="AA49" s="114" t="s">
+      <c r="AA49" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="AB49" s="114"/>
-      <c r="AC49" s="114"/>
-      <c r="AD49" s="114"/>
-      <c r="AE49" s="114"/>
-      <c r="AF49" s="114"/>
-      <c r="AG49" s="114"/>
-      <c r="AH49" s="114"/>
-      <c r="AI49" s="114"/>
-      <c r="AJ49" s="114"/>
-      <c r="AK49" s="114"/>
-      <c r="AL49" s="114"/>
-      <c r="AM49" s="114"/>
-      <c r="AN49" s="114"/>
-      <c r="AO49" s="114"/>
-      <c r="AP49" s="114"/>
-      <c r="AQ49" s="114"/>
-      <c r="AR49" s="114"/>
-      <c r="AS49" s="114"/>
-      <c r="AT49" s="114"/>
+      <c r="AB49" s="127"/>
+      <c r="AC49" s="127"/>
+      <c r="AD49" s="127"/>
+      <c r="AE49" s="127"/>
+      <c r="AF49" s="127"/>
+      <c r="AG49" s="127"/>
+      <c r="AH49" s="127"/>
+      <c r="AI49" s="127"/>
+      <c r="AJ49" s="127"/>
+      <c r="AK49" s="127"/>
+      <c r="AL49" s="127"/>
+      <c r="AM49" s="127"/>
+      <c r="AN49" s="127"/>
+      <c r="AO49" s="127"/>
+      <c r="AP49" s="127"/>
+      <c r="AQ49" s="127"/>
+      <c r="AR49" s="127"/>
+      <c r="AS49" s="127"/>
+      <c r="AT49" s="127"/>
       <c r="BB49" s="72"/>
       <c r="BC49" s="76"/>
       <c r="BD49" s="76"/>
@@ -27285,30 +29160,30 @@
       <c r="W50" s="68"/>
       <c r="X50" s="68"/>
       <c r="Y50" s="68"/>
-      <c r="AA50" s="114" t="s">
+      <c r="AA50" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="AB50" s="114"/>
-      <c r="AC50" s="114"/>
-      <c r="AD50" s="114"/>
-      <c r="AE50" s="116" t="s">
+      <c r="AB50" s="127"/>
+      <c r="AC50" s="127"/>
+      <c r="AD50" s="127"/>
+      <c r="AE50" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="AF50" s="117"/>
-      <c r="AG50" s="117"/>
-      <c r="AH50" s="117"/>
-      <c r="AI50" s="117"/>
-      <c r="AJ50" s="117"/>
-      <c r="AK50" s="117"/>
-      <c r="AL50" s="117"/>
-      <c r="AM50" s="117"/>
-      <c r="AN50" s="117"/>
-      <c r="AO50" s="117"/>
-      <c r="AP50" s="117"/>
-      <c r="AQ50" s="117"/>
-      <c r="AR50" s="117"/>
-      <c r="AS50" s="117"/>
-      <c r="AT50" s="118"/>
+      <c r="AF50" s="130"/>
+      <c r="AG50" s="130"/>
+      <c r="AH50" s="130"/>
+      <c r="AI50" s="130"/>
+      <c r="AJ50" s="130"/>
+      <c r="AK50" s="130"/>
+      <c r="AL50" s="130"/>
+      <c r="AM50" s="130"/>
+      <c r="AN50" s="130"/>
+      <c r="AO50" s="130"/>
+      <c r="AP50" s="130"/>
+      <c r="AQ50" s="130"/>
+      <c r="AR50" s="130"/>
+      <c r="AS50" s="130"/>
+      <c r="AT50" s="131"/>
       <c r="BB50" s="75"/>
       <c r="BC50" s="77"/>
       <c r="BD50" s="77"/>
@@ -27357,28 +29232,28 @@
       <c r="W51" s="68"/>
       <c r="X51" s="68"/>
       <c r="Y51" s="68"/>
-      <c r="AA51" s="114" t="s">
+      <c r="AA51" s="127" t="s">
         <v>32</v>
       </c>
-      <c r="AB51" s="114"/>
-      <c r="AC51" s="114"/>
-      <c r="AD51" s="114"/>
-      <c r="AE51" s="119"/>
-      <c r="AF51" s="115"/>
-      <c r="AG51" s="115"/>
-      <c r="AH51" s="115"/>
-      <c r="AI51" s="115"/>
-      <c r="AJ51" s="115"/>
-      <c r="AK51" s="115"/>
-      <c r="AL51" s="115"/>
-      <c r="AM51" s="115"/>
-      <c r="AN51" s="115"/>
-      <c r="AO51" s="115"/>
-      <c r="AP51" s="115"/>
-      <c r="AQ51" s="115"/>
-      <c r="AR51" s="115"/>
-      <c r="AS51" s="115"/>
-      <c r="AT51" s="120"/>
+      <c r="AB51" s="127"/>
+      <c r="AC51" s="127"/>
+      <c r="AD51" s="127"/>
+      <c r="AE51" s="132"/>
+      <c r="AF51" s="128"/>
+      <c r="AG51" s="128"/>
+      <c r="AH51" s="128"/>
+      <c r="AI51" s="128"/>
+      <c r="AJ51" s="128"/>
+      <c r="AK51" s="128"/>
+      <c r="AL51" s="128"/>
+      <c r="AM51" s="128"/>
+      <c r="AN51" s="128"/>
+      <c r="AO51" s="128"/>
+      <c r="AP51" s="128"/>
+      <c r="AQ51" s="128"/>
+      <c r="AR51" s="128"/>
+      <c r="AS51" s="128"/>
+      <c r="AT51" s="133"/>
       <c r="BB51" s="72"/>
       <c r="BC51" s="80"/>
       <c r="BD51" s="73"/>
@@ -27439,28 +29314,28 @@
       <c r="W52" s="68"/>
       <c r="X52" s="68"/>
       <c r="Y52" s="68"/>
-      <c r="AA52" s="114" t="s">
+      <c r="AA52" s="127" t="s">
         <v>33</v>
       </c>
-      <c r="AB52" s="114"/>
-      <c r="AC52" s="114"/>
-      <c r="AD52" s="114"/>
-      <c r="AE52" s="121"/>
-      <c r="AF52" s="122"/>
-      <c r="AG52" s="122"/>
-      <c r="AH52" s="122"/>
-      <c r="AI52" s="122"/>
-      <c r="AJ52" s="122"/>
-      <c r="AK52" s="122"/>
-      <c r="AL52" s="122"/>
-      <c r="AM52" s="122"/>
-      <c r="AN52" s="122"/>
-      <c r="AO52" s="122"/>
-      <c r="AP52" s="122"/>
-      <c r="AQ52" s="122"/>
-      <c r="AR52" s="122"/>
-      <c r="AS52" s="122"/>
-      <c r="AT52" s="123"/>
+      <c r="AB52" s="127"/>
+      <c r="AC52" s="127"/>
+      <c r="AD52" s="127"/>
+      <c r="AE52" s="134"/>
+      <c r="AF52" s="135"/>
+      <c r="AG52" s="135"/>
+      <c r="AH52" s="135"/>
+      <c r="AI52" s="135"/>
+      <c r="AJ52" s="135"/>
+      <c r="AK52" s="135"/>
+      <c r="AL52" s="135"/>
+      <c r="AM52" s="135"/>
+      <c r="AN52" s="135"/>
+      <c r="AO52" s="135"/>
+      <c r="AP52" s="135"/>
+      <c r="AQ52" s="135"/>
+      <c r="AR52" s="135"/>
+      <c r="AS52" s="135"/>
+      <c r="AT52" s="136"/>
       <c r="BB52" s="75"/>
       <c r="BC52" s="74"/>
       <c r="BD52" s="81"/>
@@ -27581,28 +29456,28 @@
       <c r="W54" s="68"/>
       <c r="X54" s="68"/>
       <c r="Y54" s="68"/>
-      <c r="AA54" s="114" t="s">
+      <c r="AA54" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="AB54" s="114"/>
-      <c r="AC54" s="114"/>
-      <c r="AD54" s="114"/>
-      <c r="AE54" s="114"/>
-      <c r="AF54" s="114"/>
-      <c r="AG54" s="114"/>
-      <c r="AH54" s="114"/>
-      <c r="AI54" s="114"/>
-      <c r="AJ54" s="114"/>
-      <c r="AK54" s="114"/>
-      <c r="AL54" s="114"/>
-      <c r="AM54" s="114"/>
-      <c r="AN54" s="114"/>
-      <c r="AO54" s="114"/>
-      <c r="AP54" s="114"/>
-      <c r="AQ54" s="114"/>
-      <c r="AR54" s="114"/>
-      <c r="AS54" s="114"/>
-      <c r="AT54" s="114"/>
+      <c r="AB54" s="127"/>
+      <c r="AC54" s="127"/>
+      <c r="AD54" s="127"/>
+      <c r="AE54" s="127"/>
+      <c r="AF54" s="127"/>
+      <c r="AG54" s="127"/>
+      <c r="AH54" s="127"/>
+      <c r="AI54" s="127"/>
+      <c r="AJ54" s="127"/>
+      <c r="AK54" s="127"/>
+      <c r="AL54" s="127"/>
+      <c r="AM54" s="127"/>
+      <c r="AN54" s="127"/>
+      <c r="AO54" s="127"/>
+      <c r="AP54" s="127"/>
+      <c r="AQ54" s="127"/>
+      <c r="AR54" s="127"/>
+      <c r="AS54" s="127"/>
+      <c r="AT54" s="127"/>
       <c r="BB54" s="75"/>
       <c r="BC54" s="77"/>
       <c r="BD54" s="77"/>
@@ -27651,30 +29526,30 @@
       <c r="W55" s="68"/>
       <c r="X55" s="68"/>
       <c r="Y55" s="68"/>
-      <c r="AA55" s="114" t="s">
+      <c r="AA55" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="AB55" s="114"/>
-      <c r="AC55" s="114"/>
-      <c r="AD55" s="114"/>
-      <c r="AE55" s="116" t="s">
+      <c r="AB55" s="127"/>
+      <c r="AC55" s="127"/>
+      <c r="AD55" s="127"/>
+      <c r="AE55" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="AF55" s="117"/>
-      <c r="AG55" s="117"/>
-      <c r="AH55" s="117"/>
-      <c r="AI55" s="117"/>
-      <c r="AJ55" s="117"/>
-      <c r="AK55" s="117"/>
-      <c r="AL55" s="117"/>
-      <c r="AM55" s="117"/>
-      <c r="AN55" s="117"/>
-      <c r="AO55" s="117"/>
-      <c r="AP55" s="117"/>
-      <c r="AQ55" s="117"/>
-      <c r="AR55" s="117"/>
-      <c r="AS55" s="117"/>
-      <c r="AT55" s="118"/>
+      <c r="AF55" s="130"/>
+      <c r="AG55" s="130"/>
+      <c r="AH55" s="130"/>
+      <c r="AI55" s="130"/>
+      <c r="AJ55" s="130"/>
+      <c r="AK55" s="130"/>
+      <c r="AL55" s="130"/>
+      <c r="AM55" s="130"/>
+      <c r="AN55" s="130"/>
+      <c r="AO55" s="130"/>
+      <c r="AP55" s="130"/>
+      <c r="AQ55" s="130"/>
+      <c r="AR55" s="130"/>
+      <c r="AS55" s="130"/>
+      <c r="AT55" s="131"/>
       <c r="BB55" s="72"/>
       <c r="BC55" s="80"/>
       <c r="BD55" s="73"/>
@@ -27723,28 +29598,28 @@
       <c r="W56" s="68"/>
       <c r="X56" s="68"/>
       <c r="Y56" s="68"/>
-      <c r="AA56" s="114" t="s">
+      <c r="AA56" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="AB56" s="114"/>
-      <c r="AC56" s="114"/>
-      <c r="AD56" s="114"/>
-      <c r="AE56" s="119"/>
-      <c r="AF56" s="115"/>
-      <c r="AG56" s="115"/>
-      <c r="AH56" s="115"/>
-      <c r="AI56" s="115"/>
-      <c r="AJ56" s="115"/>
-      <c r="AK56" s="115"/>
-      <c r="AL56" s="115"/>
-      <c r="AM56" s="115"/>
-      <c r="AN56" s="115"/>
-      <c r="AO56" s="115"/>
-      <c r="AP56" s="115"/>
-      <c r="AQ56" s="115"/>
-      <c r="AR56" s="115"/>
-      <c r="AS56" s="115"/>
-      <c r="AT56" s="120"/>
+      <c r="AB56" s="127"/>
+      <c r="AC56" s="127"/>
+      <c r="AD56" s="127"/>
+      <c r="AE56" s="132"/>
+      <c r="AF56" s="128"/>
+      <c r="AG56" s="128"/>
+      <c r="AH56" s="128"/>
+      <c r="AI56" s="128"/>
+      <c r="AJ56" s="128"/>
+      <c r="AK56" s="128"/>
+      <c r="AL56" s="128"/>
+      <c r="AM56" s="128"/>
+      <c r="AN56" s="128"/>
+      <c r="AO56" s="128"/>
+      <c r="AP56" s="128"/>
+      <c r="AQ56" s="128"/>
+      <c r="AR56" s="128"/>
+      <c r="AS56" s="128"/>
+      <c r="AT56" s="133"/>
       <c r="BB56" s="75"/>
       <c r="BC56" s="74"/>
       <c r="BD56" s="81"/>
@@ -27793,28 +29668,28 @@
       <c r="W57" s="68"/>
       <c r="X57" s="68"/>
       <c r="Y57" s="68"/>
-      <c r="AA57" s="114" t="s">
+      <c r="AA57" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="AB57" s="114"/>
-      <c r="AC57" s="114"/>
-      <c r="AD57" s="114"/>
-      <c r="AE57" s="121"/>
-      <c r="AF57" s="122"/>
-      <c r="AG57" s="122"/>
-      <c r="AH57" s="122"/>
-      <c r="AI57" s="122"/>
-      <c r="AJ57" s="122"/>
-      <c r="AK57" s="122"/>
-      <c r="AL57" s="122"/>
-      <c r="AM57" s="122"/>
-      <c r="AN57" s="122"/>
-      <c r="AO57" s="122"/>
-      <c r="AP57" s="122"/>
-      <c r="AQ57" s="122"/>
-      <c r="AR57" s="122"/>
-      <c r="AS57" s="122"/>
-      <c r="AT57" s="123"/>
+      <c r="AB57" s="127"/>
+      <c r="AC57" s="127"/>
+      <c r="AD57" s="127"/>
+      <c r="AE57" s="134"/>
+      <c r="AF57" s="135"/>
+      <c r="AG57" s="135"/>
+      <c r="AH57" s="135"/>
+      <c r="AI57" s="135"/>
+      <c r="AJ57" s="135"/>
+      <c r="AK57" s="135"/>
+      <c r="AL57" s="135"/>
+      <c r="AM57" s="135"/>
+      <c r="AN57" s="135"/>
+      <c r="AO57" s="135"/>
+      <c r="AP57" s="135"/>
+      <c r="AQ57" s="135"/>
+      <c r="AR57" s="135"/>
+      <c r="AS57" s="135"/>
+      <c r="AT57" s="136"/>
       <c r="BB57" s="72"/>
       <c r="BC57" s="76"/>
       <c r="BD57" s="76"/>
@@ -29621,37 +31496,37 @@
       </c>
     </row>
     <row r="20" spans="2:64" x14ac:dyDescent="0.3">
-      <c r="R20" s="124" t="s">
+      <c r="R20" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="S20" s="124"/>
-      <c r="T20" s="124"/>
-      <c r="U20" s="124"/>
-      <c r="V20" s="124"/>
-      <c r="W20" s="124"/>
-      <c r="X20" s="124"/>
-      <c r="Y20" s="124"/>
-      <c r="Z20" s="124"/>
-      <c r="AA20" s="124"/>
-      <c r="AB20" s="124"/>
-      <c r="AC20" s="124"/>
-      <c r="AD20" s="124"/>
-      <c r="AE20" s="124"/>
-      <c r="AF20" s="124"/>
-      <c r="AG20" s="124"/>
-      <c r="AH20" s="124"/>
-      <c r="AM20" s="124" t="s">
+      <c r="S20" s="137"/>
+      <c r="T20" s="137"/>
+      <c r="U20" s="137"/>
+      <c r="V20" s="137"/>
+      <c r="W20" s="137"/>
+      <c r="X20" s="137"/>
+      <c r="Y20" s="137"/>
+      <c r="Z20" s="137"/>
+      <c r="AA20" s="137"/>
+      <c r="AB20" s="137"/>
+      <c r="AC20" s="137"/>
+      <c r="AD20" s="137"/>
+      <c r="AE20" s="137"/>
+      <c r="AF20" s="137"/>
+      <c r="AG20" s="137"/>
+      <c r="AH20" s="137"/>
+      <c r="AM20" s="137" t="s">
         <v>28</v>
       </c>
-      <c r="AN20" s="124"/>
-      <c r="AO20" s="124"/>
-      <c r="AP20" s="124"/>
-      <c r="AQ20" s="124"/>
-      <c r="AR20" s="124"/>
-      <c r="AS20" s="124"/>
-      <c r="AT20" s="124"/>
-      <c r="AU20" s="124"/>
-      <c r="AV20" s="124"/>
+      <c r="AN20" s="137"/>
+      <c r="AO20" s="137"/>
+      <c r="AP20" s="137"/>
+      <c r="AQ20" s="137"/>
+      <c r="AR20" s="137"/>
+      <c r="AS20" s="137"/>
+      <c r="AT20" s="137"/>
+      <c r="AU20" s="137"/>
+      <c r="AV20" s="137"/>
     </row>
     <row r="21" spans="2:64" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -30787,18 +32662,18 @@
       <c r="BL43" s="2"/>
     </row>
     <row r="44" spans="2:64" x14ac:dyDescent="0.3">
-      <c r="C44" s="124" t="s">
+      <c r="C44" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="124"/>
-      <c r="G44" s="124"/>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="124"/>
-      <c r="L44" s="124"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="137"/>
+      <c r="H44" s="137"/>
+      <c r="I44" s="137"/>
+      <c r="J44" s="137"/>
+      <c r="K44" s="137"/>
+      <c r="L44" s="137"/>
       <c r="S44" s="3">
         <v>12</v>
       </c>
@@ -31641,18 +33516,18 @@
       </c>
     </row>
     <row r="59" spans="10:64" x14ac:dyDescent="0.3">
-      <c r="AL59" s="124" t="s">
+      <c r="AL59" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="AM59" s="124"/>
-      <c r="AN59" s="124"/>
-      <c r="AO59" s="124"/>
-      <c r="AP59" s="124"/>
-      <c r="AQ59" s="124"/>
-      <c r="AR59" s="124"/>
-      <c r="AS59" s="124"/>
-      <c r="AT59" s="124"/>
-      <c r="AU59" s="124"/>
+      <c r="AM59" s="137"/>
+      <c r="AN59" s="137"/>
+      <c r="AO59" s="137"/>
+      <c r="AP59" s="137"/>
+      <c r="AQ59" s="137"/>
+      <c r="AR59" s="137"/>
+      <c r="AS59" s="137"/>
+      <c r="AT59" s="137"/>
+      <c r="AU59" s="137"/>
     </row>
     <row r="62" spans="10:64" ht="19.8" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="63" spans="10:64" x14ac:dyDescent="0.3">
@@ -32032,13 +33907,13 @@
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
-      <c r="O77" s="131"/>
+      <c r="O77" s="118"/>
       <c r="P77" s="1"/>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
-      <c r="AM77" s="134"/>
+      <c r="AM77" s="120"/>
       <c r="AN77" s="1"/>
     </row>
     <row r="78" spans="10:42" x14ac:dyDescent="0.3">
@@ -32046,13 +33921,13 @@
         <v>6</v>
       </c>
       <c r="K78" s="1"/>
-      <c r="L78" s="131"/>
+      <c r="L78" s="118"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
       <c r="P78" s="1"/>
       <c r="AI78" s="1"/>
-      <c r="AJ78" s="134"/>
+      <c r="AJ78" s="120"/>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
       <c r="AM78" s="1"/>
@@ -32073,7 +33948,7 @@
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
       <c r="AM79" s="1"/>
-      <c r="AN79" s="134"/>
+      <c r="AN79" s="120"/>
     </row>
     <row r="80" spans="10:42" x14ac:dyDescent="0.3">
       <c r="J80" s="3" t="s">
@@ -32087,7 +33962,7 @@
       <c r="P80" s="1"/>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
-      <c r="AK80" s="134"/>
+      <c r="AK80" s="120"/>
       <c r="AL80" s="1"/>
       <c r="AM80" s="1"/>
       <c r="AN80" s="1"/>
@@ -32105,7 +33980,7 @@
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
-      <c r="AL81" s="134"/>
+      <c r="AL81" s="120"/>
       <c r="AM81" s="1"/>
       <c r="AN81" s="1"/>
     </row>
@@ -32119,7 +33994,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
-      <c r="AI82" s="134"/>
+      <c r="AI82" s="120"/>
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
@@ -32146,13 +34021,13 @@
       <c r="AH84" s="3">
         <v>8</v>
       </c>
-      <c r="AI84" s="132"/>
+      <c r="AI84" s="1"/>
       <c r="AJ84" s="94"/>
-      <c r="AK84" s="131"/>
-      <c r="AL84" s="132"/>
+      <c r="AK84" s="118"/>
+      <c r="AL84" s="1"/>
       <c r="AM84" s="94"/>
-      <c r="AN84" s="131"/>
-      <c r="AP84" s="132"/>
+      <c r="AN84" s="118"/>
+      <c r="AP84" s="1"/>
     </row>
     <row r="85" spans="10:46" x14ac:dyDescent="0.3">
       <c r="J85" s="3">
@@ -32173,13 +34048,13 @@
       <c r="AH85" s="3">
         <v>7</v>
       </c>
-      <c r="AI85" s="131"/>
+      <c r="AI85" s="118"/>
       <c r="AJ85" s="94"/>
-      <c r="AK85" s="132"/>
-      <c r="AL85" s="131"/>
+      <c r="AK85" s="1"/>
+      <c r="AL85" s="118"/>
       <c r="AM85" s="94"/>
-      <c r="AN85" s="132"/>
-      <c r="AP85" s="131"/>
+      <c r="AN85" s="1"/>
+      <c r="AP85" s="118"/>
       <c r="AT85" s="3" t="s">
         <v>58</v>
       </c>
@@ -32203,13 +34078,13 @@
       <c r="AH86" s="3">
         <v>6</v>
       </c>
-      <c r="AI86" s="132"/>
-      <c r="AJ86" s="132"/>
-      <c r="AK86" s="131"/>
-      <c r="AL86" s="132"/>
-      <c r="AM86" s="132"/>
-      <c r="AN86" s="131"/>
-      <c r="AP86" s="132"/>
+      <c r="AI86" s="1"/>
+      <c r="AJ86" s="1"/>
+      <c r="AK86" s="118"/>
+      <c r="AL86" s="1"/>
+      <c r="AM86" s="1"/>
+      <c r="AN86" s="118"/>
+      <c r="AP86" s="1"/>
     </row>
     <row r="87" spans="10:46" x14ac:dyDescent="0.3">
       <c r="J87" s="3">
@@ -32230,13 +34105,13 @@
       <c r="AH87" s="3">
         <v>5</v>
       </c>
-      <c r="AI87" s="131"/>
-      <c r="AJ87" s="132"/>
-      <c r="AK87" s="132"/>
-      <c r="AL87" s="131"/>
-      <c r="AM87" s="132"/>
-      <c r="AN87" s="132"/>
-      <c r="AP87" s="131"/>
+      <c r="AI87" s="118"/>
+      <c r="AJ87" s="1"/>
+      <c r="AK87" s="1"/>
+      <c r="AL87" s="118"/>
+      <c r="AM87" s="1"/>
+      <c r="AN87" s="1"/>
+      <c r="AP87" s="118"/>
     </row>
     <row r="88" spans="10:46" x14ac:dyDescent="0.3">
       <c r="J88" s="3">
@@ -32260,13 +34135,13 @@
       <c r="AH88" s="3">
         <v>4</v>
       </c>
-      <c r="AI88" s="133"/>
+      <c r="AI88" s="119"/>
       <c r="AJ88" s="102"/>
-      <c r="AK88" s="133"/>
-      <c r="AL88" s="133"/>
+      <c r="AK88" s="119"/>
+      <c r="AL88" s="119"/>
       <c r="AM88" s="102"/>
-      <c r="AN88" s="133"/>
-      <c r="AP88" s="133"/>
+      <c r="AN88" s="119"/>
+      <c r="AP88" s="119"/>
     </row>
     <row r="89" spans="10:46" x14ac:dyDescent="0.3">
       <c r="J89" s="3">
@@ -32290,13 +34165,13 @@
       <c r="AH89" s="3">
         <v>3</v>
       </c>
-      <c r="AI89" s="133"/>
+      <c r="AI89" s="119"/>
       <c r="AJ89" s="102"/>
-      <c r="AK89" s="133"/>
-      <c r="AL89" s="133"/>
+      <c r="AK89" s="119"/>
+      <c r="AL89" s="119"/>
       <c r="AM89" s="102"/>
-      <c r="AN89" s="133"/>
-      <c r="AP89" s="133"/>
+      <c r="AN89" s="119"/>
+      <c r="AP89" s="119"/>
     </row>
     <row r="90" spans="10:46" x14ac:dyDescent="0.3">
       <c r="J90" s="3">
@@ -32317,13 +34192,13 @@
       <c r="AH90" s="3">
         <v>2</v>
       </c>
-      <c r="AI90" s="132"/>
-      <c r="AJ90" s="132"/>
-      <c r="AK90" s="131"/>
-      <c r="AL90" s="132"/>
-      <c r="AM90" s="132"/>
-      <c r="AN90" s="131"/>
-      <c r="AP90" s="132"/>
+      <c r="AI90" s="1"/>
+      <c r="AJ90" s="1"/>
+      <c r="AK90" s="118"/>
+      <c r="AL90" s="1"/>
+      <c r="AM90" s="1"/>
+      <c r="AN90" s="118"/>
+      <c r="AP90" s="1"/>
     </row>
     <row r="91" spans="10:46" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J91" s="3">
@@ -32344,13 +34219,13 @@
       <c r="AH91" s="3">
         <v>1</v>
       </c>
-      <c r="AI91" s="131"/>
-      <c r="AJ91" s="132"/>
-      <c r="AK91" s="132"/>
-      <c r="AL91" s="131"/>
-      <c r="AM91" s="132"/>
-      <c r="AN91" s="132"/>
-      <c r="AP91" s="131"/>
+      <c r="AI91" s="118"/>
+      <c r="AJ91" s="1"/>
+      <c r="AK91" s="1"/>
+      <c r="AL91" s="118"/>
+      <c r="AM91" s="1"/>
+      <c r="AN91" s="1"/>
+      <c r="AP91" s="118"/>
     </row>
     <row r="92" spans="10:46" x14ac:dyDescent="0.3">
       <c r="J92" s="3" t="s">
@@ -32941,20 +34816,20 @@
       <c r="BB25" s="2"/>
     </row>
     <row r="26" spans="2:54" x14ac:dyDescent="0.3">
-      <c r="G26" s="124" t="s">
+      <c r="G26" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="124"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="124"/>
-      <c r="K26" s="124"/>
-      <c r="L26" s="124"/>
-      <c r="M26" s="124"/>
-      <c r="N26" s="124"/>
-      <c r="O26" s="124"/>
-      <c r="P26" s="124"/>
-      <c r="Q26" s="124"/>
-      <c r="R26" s="124"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="137"/>
+      <c r="K26" s="137"/>
+      <c r="L26" s="137"/>
+      <c r="M26" s="137"/>
+      <c r="N26" s="137"/>
+      <c r="O26" s="137"/>
+      <c r="P26" s="137"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="137"/>
       <c r="AP26" s="3">
         <v>4</v>
       </c>
@@ -33091,20 +34966,20 @@
       <c r="L31" s="84"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="AQ31" s="114" t="s">
+      <c r="AQ31" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="AR31" s="114"/>
-      <c r="AS31" s="114"/>
-      <c r="AT31" s="114"/>
-      <c r="AU31" s="114"/>
-      <c r="AX31" s="114" t="s">
+      <c r="AR31" s="127"/>
+      <c r="AS31" s="127"/>
+      <c r="AT31" s="127"/>
+      <c r="AU31" s="127"/>
+      <c r="AX31" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="AY31" s="114"/>
-      <c r="AZ31" s="114"/>
-      <c r="BA31" s="114"/>
-      <c r="BB31" s="114"/>
+      <c r="AY31" s="127"/>
+      <c r="AZ31" s="127"/>
+      <c r="BA31" s="127"/>
+      <c r="BB31" s="127"/>
     </row>
     <row r="32" spans="2:54" x14ac:dyDescent="0.3">
       <c r="D32" s="3">
